--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +208,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Guaranty Trust Bank (UK) Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Guaranty Trust Bank (UK) Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -389,13 +394,511 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Guaranty Trust Bank (UK) Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Guaranty Trust Bank (UK) Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$22:$AL$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$23:$AL$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$22:$AL$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$22:$AL$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$22:$AL$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -408,6 +911,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -705,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -728,6 +1297,24 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,14 +1327,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£)</t>
+          <t>Balance Sheet Summary (£)</t>
         </is>
       </c>
     </row>
@@ -811,160 +1398,648 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n">
-        <v>57935255</v>
+        <v>583445887</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-102327202</v>
+        <v>470783450</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>117737509</v>
+        <v>626844615</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>52298689</v>
+        <v>490836145</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>52298689</v>
+        <v>490836145</v>
       </c>
       <c r="K6" t="n">
-        <v>117737509</v>
+        <v>626844615</v>
       </c>
       <c r="L6" t="n">
-        <v>-102327202</v>
+        <v>470783450</v>
       </c>
       <c r="M6" t="n">
-        <v>57935255</v>
+        <v>583445887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n">
-        <v>11837282</v>
+        <v>62534590</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-38512179</v>
+        <v>57675796</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-26064114</v>
+        <v>61872149</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-17917411</v>
+        <v>57660949</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-17917411</v>
+        <v>57660949</v>
       </c>
       <c r="K7" t="n">
-        <v>-26064114</v>
+        <v>61872149</v>
       </c>
       <c r="L7" t="n">
-        <v>-38512179</v>
+        <v>57675796</v>
       </c>
       <c r="M7" t="n">
-        <v>11837282</v>
+        <v>62534590</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) financing activities</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n">
-        <v>-705754</v>
+        <v>535370508</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-570000</v>
+        <v>431392457</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-1892429</v>
+        <v>598500237</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-1411693</v>
+        <v>465746504</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) financing activities</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-1411693</v>
+        <v>465746504</v>
       </c>
       <c r="K8" t="n">
-        <v>-1892429</v>
+        <v>598500237</v>
       </c>
       <c r="L8" t="n">
-        <v>-570000</v>
+        <v>431392457</v>
       </c>
       <c r="M8" t="n">
-        <v>-705754</v>
+        <v>535370508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Shareholders' funds (Total equity)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n">
-        <v>308066190</v>
+        <v>48075379</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>238999407</v>
+        <v>39390993</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>380408788</v>
+        <v>28344378</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>116275570</v>
+        <v>25089641</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Shareholders' funds (Total equity)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>116275570</v>
+        <v>25089641</v>
       </c>
       <c r="K9" t="n">
-        <v>380408788</v>
+        <v>28344378</v>
       </c>
       <c r="L9" t="n">
-        <v>238999407</v>
+        <v>39390993</v>
       </c>
       <c r="M9" t="n">
-        <v>308066190</v>
+        <v>48075379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Profit &amp; Loss Summary (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>25709803</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>27461859</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>17528715</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7426157</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>7426157</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17528715</v>
+      </c>
+      <c r="T13" t="n">
+        <v>27461859</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25709803</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>-14155063</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-13536374</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-12466246</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-17318100</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-17318100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-12466246</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-13536374</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-14155063</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-8329814</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>-8329814</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8638639</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total equity, end of year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>25089641</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Total equity, end of year</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>25089641</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>48075379</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n">
+        <v>57935255</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-102327202</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>117737509</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>52298689</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>52298689</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>117737509</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-102327202</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>57935255</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n">
+        <v>11837282</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-38512179</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-26064114</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-17917411</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>-17917411</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-26064114</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>-38512179</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>11837282</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n">
+        <v>-705754</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-1411693</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>-1411693</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-705754</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n">
+        <v>308066190</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>116275570</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>116275570</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>308066190</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Pillar 3 Key Metrics: not applicable — no ratios are disclosed for this entity (see the individual Pillar 3 metric sheets).</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Note: No Pillar 3 ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR/MREL) are disclosed for this entity at all - only a single £ regulatory-capital figure (see the CET1/Tier 1/Total Capital sheets). Figures above are duplicated from the Cash Flow Statement sheet for at-a-glance trend viewing; see that sheet's own source citation, including a flagged FY2021/FY2022 basis discontinuity in the cash-equivalents figures.</t>
         </is>
@@ -972,7 +2047,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -999,7 +2074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
@@ -1041,7 +2116,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Leverage Ratio</t>
+          <t>Tier 1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1104,10 +2179,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1118,12 +2193,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1160,37 +2239,32 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Total regulatory capital (unaudited)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
 Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
@@ -1210,8 +2284,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1237,7 +2312,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -1279,7 +2354,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>Total Capital Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1356,7 +2431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
         </is>
       </c>
     </row>
@@ -1398,7 +2473,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>Total RWAs</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1455,7 +2530,2030 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
+Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
+sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
+personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
+page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
+disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
+only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
+'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
+Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
+FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
+Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
+sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
+personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
+page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
+disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
+only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
+'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
+Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
+FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>LCR</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
+Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
+sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
+personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
+page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
+disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
+only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
+'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
+Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
+FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>NSFR</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
+Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
+sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
+personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
+page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
+disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
+only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
+'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
+Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
+FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
+Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
+sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
+personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
+page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
+disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
+only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
+'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
+Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
+FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Cash and money market funds</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>100662477</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>94365231</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>97716359</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>116275570</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>259678468</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>152612406</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>345107924</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>230460594</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>62534590</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>57675796</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>61872149</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>57660949</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Investment securities</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>146470054</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>151922722</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>107015424</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>82190414</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>3746354</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3197915</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2292269</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>691135</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Right-of-use leasehold property</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>9777616</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>10556149</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>11599109</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>616484</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>567044</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>440852</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>291795</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>898439</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>9284</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>12379</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>949586</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2042560</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>583445887</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>470783450</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>626844615</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>490836145</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Deposits by banks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n">
+        <v>329988520</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>217403953</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>344658275</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>291426385</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Deposits by customers</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>191532438</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>196877072</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>232269660</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>163962244</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Leasehold liability</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>10765913</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>11061158</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>11215172</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>704605</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n">
+        <v>2832498</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>5875018</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>10338218</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>9598620</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>251139</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>175256</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>18912</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>54650</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>535370508</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>431392457</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>598500237</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>465746504</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>11019326</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>2380687</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-8026214</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-11900852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Fair value reserves</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Shareholders' funds (Total equity)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and shareholders' funds</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n">
+        <v>583445887</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>470783450</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>626844615</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>490836145</v>
+      </c>
+    </row>
+    <row r="29" ht="260" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
+FY2023-FY2024 and 'Cash and cash equivalents' FY2021-FY2022 - same line, presentation relabelled;
+shown on separate rows above rather than merged, to match each year's own disclosed label.
+Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
+Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>26095367</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>24585386</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>12096324</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3155907</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>-8140535</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>-5078320</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-1902227</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>-780155</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>17954832</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>19507066</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>10194097</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2375752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Fees and commissions income</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>3222120</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>3544250</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3569967</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2462438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>4532851</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>4410543</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3764651</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>2587967</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>25709803</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>27461859</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>17528715</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7426157</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Personnel expenses</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>-8202750</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>-8017084</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>-5831341</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>-5096462</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>-1370575</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>-1560012</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>-2176624</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>-1569766</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>-4581738</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-3959278</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-4458281</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>-10651872</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>-14155063</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-13536374</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-12466246</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-17318100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>180144</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>176822</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Rental income</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>20786</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit impairment losses (charge)/reversal</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>-74019</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>12663</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-120728</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>-17516</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) before taxation</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>11480721</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>13958934</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5121885</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-9732637</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Taxation (charge)/credit</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>-2842082</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>-3552033</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-1247247</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1402823</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the year</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-8329814</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income, net of corporation tax</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain/(loss) on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-6686</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Fair value (gain)/loss reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>-10306</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>629408</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>9507</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n">
+        <v>8684386</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>11046615</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>3254737</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-8346007</v>
+      </c>
+    </row>
+    <row r="27" ht="200" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
+Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological roll-forward, oldest to newest. Equity reconciliation ladder confirmed: each year's own closing balance ties exactly to the next year's own opening balance and to that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Fair value reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>-3571038</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>6686</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>33435648</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Net change in fair value</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Net amount reclassified to P&amp;L</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11900852</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Fair value (loss) on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Net profit/(loss) reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n">
+        <v>9507</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9507</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-8026214</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>28344378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>10306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Fair value loss reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>629408</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>629408</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2380687</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>39390993</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>56053</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>11019326</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>48075379</v>
+      </c>
+    </row>
+    <row r="22" ht="200" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
+Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2191,7 +5289,389 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loan book by maturity band and Expected Credit Loss (ECL) allowance, as originally published each year. The Bank does not disclose an IFRS 9 Stage 1/2/3 split anywhere in its Annual Report - only a single aggregate ECL figure per loan category - confirmed by reading Notes 12/13 and Note 23 (credit risk) in full each year; see source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>207403713</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>144634176</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>335020113</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>218116770</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>52375036</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>8003078</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>10166817</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>12416941</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>-100281</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-24848</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-79006</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>-73117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>259678468</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>152612406</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>345107924</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>230460594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>1784014</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1022971</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1040567</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1416091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>5175504</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4571746</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6260705</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4406409</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Five years or less but over one year</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>17362794</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>15880590</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>15958829</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>16188919</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Over five years</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>38770629</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>36660770</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>39112659</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>35959033</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Less: Deferred Mortgage Arrangement Fees (EIR liability)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>-532746</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-437081</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-389084</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>-307451</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>-25605</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>-23200</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-111527</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>-2052</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>62534590</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>57675796</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>61872149</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>57660949</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios (not directly disclosed, computed for reference)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ECL coverage - loans and advances to customers (ECL / gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="210" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
+Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2297,482 +5777,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Tier 1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Total regulatory capital (unaudited)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2798,7 +5802,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -2840,7 +5844,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
+          <t>CET1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -2903,10 +5907,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2917,12 +5921,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2959,37 +5967,32 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
 Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
@@ -3009,8 +6012,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -612,7 +612,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -655,8 +655,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -695,13 +695,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -738,7 +738,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -762,7 +762,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -786,7 +786,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -853,8 +853,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -893,7 +893,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -908,9 +908,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -930,9 +930,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -952,9 +952,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -974,9 +974,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2063,7 +2063,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2079,7 +2079,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2116,50 +2120,42 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>26.89%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>32.30%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>20.68%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2266,18 +2262,14 @@
     <row r="7" ht="170" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2301,7 +2293,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2317,7 +2309,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2357,47 +2353,39 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>26.89%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>32.30%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>20.68%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2420,7 +2408,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2436,7 +2424,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2476,47 +2468,31 @@
           <t>Total RWAs</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>157370</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>105275</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2536,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2557,7 +2533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Not publicly disclosed. See source note at bottom.</t>
+          <t>Standalone Pillar 3 disclosures, £'000.</t>
         </is>
       </c>
     </row>
@@ -2596,30 +2572,62 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Credit risk RWA</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+      <c r="E4" s="7" t="n">
+        <v>166793</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>77962</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>20026</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>22148</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" ht="280" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2627,7 +2635,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2642,7 +2650,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2658,7 +2666,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2698,47 +2710,39 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>8.30%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+          <t>5.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2761,7 +2765,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2777,7 +2781,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2814,50 +2822,42 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>309%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>250%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>274%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+          <t>356%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -2877,10 +2877,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2896,7 +2896,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2933,58 +2937,50 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>NSFR</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>260%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>310%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: The FY2022 standalone disclosure does not report an NSFR figure; FY2021 is not substituted from another entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3084,18 +3080,14 @@
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -5757,18 +5749,14 @@
     <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -5791,7 +5779,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -5807,7 +5795,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5844,50 +5836,42 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>26.89%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>32.30%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>20.68%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>
@@ -5994,18 +5978,14 @@
     <row r="7" ht="170" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited does not publish a standalone Pillar 3 disclosure document.
-Confirmed via a full enumeration of every URL in gtbankuk.com's own sitemap.xml (all 8 sitemap
-sections: about, businessBanking, helpCentre, homepage, investorRelationsIndex, mediaCentre,
-personalBanking, securityCentre, staticPages) - no Pillar 3, regulatory-disclosures, or capital-ratio
-page/document exists anywhere on the site. The Strategic Report each year states that Pillar 3/CRD IV
-disclosures are 'set out in the Directors' Report' and risk management policies 'in Note 23', but the
-only quantitative capital figure actually given anywhere in the statutory accounts is Note 23.8(a)
-'Regulatory capital (unaudited)', reproduced below. No CET1/Total Capital/Leverage ratio, RWA,
-Leverage Ratio, LCR, NSFR, or MREL figure of any kind is disclosed for any year.
-FY2024/FY2023: Annual Report FY2024, Note 23.8(a) 'Regulatory capital (unaudited)', p.68 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report FY2022, Note 23.8(a) 'Regulatory capital (unaudited)', p.62 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-(FY2021's own figure is confirmed identical in both the FY2021 Annual Report's own Note 23.8(a), p.58 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0 - and the FY2022 Annual Report's FY2021 comparative column.)
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
+CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
+MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
+the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
 regulatory capital throughout; the same figure is used on all three sheets below.</t>
         </is>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -612,7 +612,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -655,8 +655,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -695,13 +695,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -738,7 +738,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -762,7 +762,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -786,7 +786,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -853,8 +853,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -893,7 +893,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -908,9 +908,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -930,9 +930,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -952,9 +952,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -974,9 +974,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2426,7 +2426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standalone Pillar 3 disclosures, £'000.</t>
+          <t>Standalone Pillar 3 disclosures, £'000. Component split is reported for FY2022/FY2021; FY2024/FY2023 reports disclose only total RWA.</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Investment securities</t>
+          <t>Investment securities (FVOCI - government securities, 100% UK/US/Belgium sovereign)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -3618,6 +3618,11 @@
           <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
 FY2023-FY2024 and 'Cash and cash equivalents' FY2021-FY2022 - same line, presentation relabelled;
 shown on separate rows above rather than merged, to match each year's own disclosed label.
+Investment securities note (Note 14, 'Investment securities'): all years' Annual Reports disclose the
+entire book as held at Fair Value through Other Comprehensive Income (FVOCI), with the Bank stating no
+financial assets are held at amortised cost or FVTPL, and as securities issued solely by government
+institutions (UK, US and, per the FY2024 Annual Report, Belgium) - FY2024: p.46; FY2022/FY2021: p.43
+of the FY2022 Annual Report (Note 14).
 Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
 each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
 FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -2041,7 +2041,7 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Note: No Pillar 3 ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR/MREL) are disclosed for this entity at all - only a single £ regulatory-capital figure (see the CET1/Tier 1/Total Capital sheets). Figures above are duplicated from the Cash Flow Statement sheet for at-a-glance trend viewing; see that sheet's own source citation, including a flagged FY2021/FY2022 basis discontinuity in the cash-equivalents figures.</t>
+          <t>Note: Pillar 3 ratios ARE disclosed for this entity (CET1/Tier 1/Total Capital ratio, leverage ratio, LCR, and NSFR from FY2023) - see those individual metric sheets; only MREL is never numerically disclosed. They are not repeated in the ratio block above. The statutory-statement figures above are blank for FY2025 because no FY2025 Annual Report has been filed with Companies House yet (next due 30 Sep 2026), even though the FY2025 Pillar 3 disclosure has been published - so the Pillar 3 sheets do carry a full FY2025 column. Figures above are duplicated from the Cash Flow Statement sheet for at-a-glance trend viewing; see that sheet's own source citation, including a flagged FY2021/FY2022 basis discontinuity in the cash-equivalents figures.</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2120,10 +2120,14 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+          <t>Tier 1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>26.89%</t>
@@ -2131,38 +2135,121 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>32.30%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2238,7 +2325,9 @@
           <t>Total regulatory capital (unaudited)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
       <c r="C4" s="7" t="n">
         <v>48075379</v>
       </c>
@@ -2263,15 +2352,74 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2350,10 +2498,14 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+          <t>Total Capital Ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>26.89%</t>
@@ -2361,38 +2513,121 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>32.30%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2405,7 +2640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2465,10 +2700,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+          <t>Total risk-weighted exposure amount (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>148821</v>
+      </c>
       <c r="C4" s="7" t="n">
         <v>157370</v>
       </c>
@@ -2482,24 +2719,105 @@
         <v>100287</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n">
+        <v>108387</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2512,7 +2830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2533,7 +2851,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standalone Pillar 3 disclosures, £'000. Component split is reported for FY2022/FY2021; FY2024/FY2023 reports disclose only total RWA.</t>
+          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5 - see the two SECTION blocks below and the sources note. FY2023: no reliable risk-type breakdown recoverable - see sources note.</t>
         </is>
       </c>
     </row>
@@ -2570,72 +2888,175 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n">
-        <v>166793</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>77962</v>
-      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Operational risk RWA</t>
+          <t>Credit risk RWA</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n">
-        <v>20026</v>
+        <v>166793</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>22148</v>
+        <v>77962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Market risk RWA</t>
+          <t>Operational risk RWA</t>
         </is>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n">
+        <v>20026</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>22148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
         <v>215</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F7" s="7" t="n">
         <v>177</v>
       </c>
     </row>
-    <row r="8" ht="280" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>98212.5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>113012.5</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>50337.5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>44187.5</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>148825</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>157375</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="15" ht="280" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
+FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
+(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
+(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
+(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2647,7 +3068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2707,10 +3128,14 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Leverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+          <t>Leverage Ratio (as first published in each year's own Pillar 3 report)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>9.11%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>8.02%</t>
@@ -2718,39 +3143,142 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>8.29%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>8.30%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>4.38%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
+  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
+  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
+  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
+FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2762,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2825,7 +3353,11 @@
           <t>Liquidity Coverage Ratio</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>197%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>309%</t>
@@ -2847,25 +3379,94 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
+DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
+By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2940,7 +3541,11 @@
           <t>Net Stable Funding Ratio</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>211%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>260%</t>
@@ -2951,13 +3556,19 @@
           <t>310%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>253%</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Note: The FY2022 standalone disclosure does not report an NSFR figure; FY2021 is not substituted from another entity.</t>
+          <t>Note: FY2022 (253%) was added 2026-09-15. The FY2022 Pillar 3 report itself never mentions NSFR at all (the string does not occur in the document), but the FY2023 report's Key Metrics table carries a full FY2022 comparative column for it - Total available stable funding 214,036 / Total required stable funding 84,527 (GBP'000), printed ratio 253%. That is the Bank's own figure for its own entity, on the same basis as every other year on this sheet, so it is transcribed here; the same comparative-column convention is already used for FY2021 elsewhere in this workbook.
+FY2021 remains blank: no NSFR is disclosed for it in any reviewed edition, and nothing is substituted from another entity.
+Unlike the LCR sheet, the NSFR components reconcile to the printed ratio exactly in every disclosed year: FY2025 198,459 / 94,033 = 211%; FY2024 200,729 / 77,347 = 260%; FY2023 194,572 / 62,864 = 310%; FY2022 214,036 / 84,527 = 253% (GBP'000).</t>
         </is>
       </c>
     </row>
@@ -2965,15 +3576,74 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
@@ -3081,15 +3751,74 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
@@ -3636,8 +4365,17 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
-Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
 DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
 'cash and cash equivalents for 2021 have been re-presented to include money market placements with
 maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
@@ -4148,8 +4886,17 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
-Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
 DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
 'cash and cash equivalents for 2021 have been re-presented to include money market placements with
 maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
@@ -4523,8 +5270,17 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
-Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
 DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
 'cash and cash equivalents for 2021 have been re-presented to include money market placements with
 maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
@@ -5259,8 +6015,17 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
-Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
 DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
 'cash and cash equivalents for 2021 have been re-presented to include money market placements with
 maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
@@ -5641,8 +6406,17 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required. FY2025 accounts (year ended 31 Dec 2025) had not yet been filed with
-Companies House as of this build (last filing: FY2024, filed 6 May 2025); FY2025 is left blank.
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
 DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
 'cash and cash equivalents for 2021 have been re-presented to include money market placements with
 maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
@@ -5737,7 +6511,9 @@
           <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
       <c r="C4" s="7" t="n">
         <v>48075379</v>
       </c>
@@ -5755,15 +6531,74 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
@@ -5781,7 +6616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5841,10 +6676,14 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+          <t>CET1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>26.89%</t>
@@ -5852,38 +6691,121 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CET1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>32.30%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5959,7 +6881,9 @@
           <t>Tier 1 capital</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
       <c r="C4" s="7" t="n">
         <v>48075379</v>
       </c>
@@ -5984,15 +6908,74 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
 FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: Key Metrics pp.13-14, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
 FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure. These disclosures provide
-CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR and (from FY2023) NSFR.
-MREL is not numerically disclosed in the reviewed standalone reports. FY2024/FY2023 also cross-check
-the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
 The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.</t>
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
         </is>
       </c>
     </row>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2060,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2074,14 +2075,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£</t>
         </is>
       </c>
     </row>
@@ -2120,60 +2121,34 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2249,8 +2224,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2262,7 +2237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2276,14 +2251,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2322,34 +2297,60 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total regulatory capital (unaudited)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604000</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Tier 1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2425,8 +2426,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2438,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2452,14 +2453,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£</t>
         </is>
       </c>
     </row>
@@ -2498,60 +2499,34 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total Capital Ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+          <t>Total regulatory capital (unaudited)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2627,8 +2602,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2654,14 +2629,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2700,35 +2675,47 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>148821</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>157370</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>105275</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>100287</v>
+          <t>Total Capital Ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n">
-        <v>108387</v>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
@@ -2736,7 +2723,7 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
         </is>
       </c>
     </row>
@@ -2830,245 +2817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5 - see the two SECTION blocks below and the sources note. FY2023: no reliable risk-type breakdown recoverable - see sources note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£'000)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n">
-        <v>166793</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>77962</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>20026</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>22148</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n">
-        <v>215</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>100287</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>98212.5</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>113012.5</v>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>275</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>50337.5</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>44187.5</v>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>148825</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>157375</v>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="15" ht="280" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
-FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
-(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
-(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
-(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3082,14 +2831,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3128,80 +2877,48 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Leverage Ratio (as first published in each year's own Pillar 3 report)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>9.11%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>8.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>4.38%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
+          <t>Total risk-weighted exposure amount (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>148821</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>157370</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>105275</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>100287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>8.30%</t>
-        </is>
+      <c r="D5" s="7" t="n">
+        <v>108387</v>
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
-  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
-  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
-  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
-FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -3277,8 +2994,246 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5 - see the two SECTION blocks below and the sources note. FY2023: no reliable risk-type breakdown recoverable - see sources note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>166793</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>77962</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>20026</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>22148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>98212.5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>113012.5</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>50337.5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>44187.5</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>148825</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>157375</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="15" ht="280" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
+FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
+(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
+(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
+(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3290,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3304,7 +3259,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -3350,46 +3305,80 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
+          <t>Leverage Ratio (as first published in each year's own Pillar 3 report)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>197%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>309%</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>250%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>274%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>356%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
-DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
-By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>5.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>8.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
+  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
+  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
+  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
+FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -3465,8 +3454,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3492,7 +3481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
+          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -3538,37 +3527,41 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
+          <t>Liquidity Coverage Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>211%</t>
+          <t>197%</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>260%</t>
+          <t>309%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>310%</t>
+          <t>250%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>253%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n"/>
+          <t>274%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>356%</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Note: FY2022 (253%) was added 2026-09-15. The FY2022 Pillar 3 report itself never mentions NSFR at all (the string does not occur in the document), but the FY2023 report's Key Metrics table carries a full FY2022 comparative column for it - Total available stable funding 214,036 / Total required stable funding 84,527 (GBP'000), printed ratio 253%. That is the Bank's own figure for its own entity, on the same basis as every other year on this sheet, so it is transcribed here; the same comparative-column convention is already used for FY2021 elsewhere in this workbook.
-FY2021 remains blank: no NSFR is disclosed for it in any reviewed edition, and nothing is substituted from another entity.
-Unlike the LCR sheet, the NSFR components reconcile to the printed ratio exactly in every disclosed year: FY2025 198,459 / 94,033 = 211%; FY2024 200,729 / 77,347 = 260%; FY2023 194,572 / 62,864 = 310%; FY2022 214,036 / 84,527 = 253% (GBP'000).</t>
+          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
+DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
+By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
         </is>
       </c>
     </row>
@@ -3662,10 +3655,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3676,12 +3669,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3718,37 +3715,42 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>Net Stable Funding Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>211%</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>260%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>310%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>253%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2022 (253%) was added 2026-09-15. The FY2022 Pillar 3 report itself never mentions NSFR at all (the string does not occur in the document), but the FY2023 report's Key Metrics table carries a full FY2022 comparative column for it - Total available stable funding 214,036 / Total required stable funding 84,527 (GBP'000), printed ratio 253%. That is the Bank's own figure for its own entity, on the same basis as every other year on this sheet, so it is transcribed here; the same comparative-column convention is already used for FY2021 elsewhere in this workbook.
+FY2021 remains blank: no NSFR is disclosed for it in any reviewed edition, and nothing is substituted from another entity.
+Unlike the LCR sheet, the NSFR components reconcile to the printed ratio exactly in every disclosed year: FY2025 198,459 / 94,033 = 211%; FY2024 200,729 / 77,347 = 260%; FY2023 194,572 / 62,864 = 310%; FY2022 214,036 / 84,527 = 253% (GBP'000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -3823,23 +3825,24 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3850,2684 +3853,78 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Financial Position</t>
+          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As originally published in each year's own Annual Report</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Line item</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025 (£)</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024 (£)</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023 (£)</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022 (£)</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Cash and money market funds</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>100662477</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>94365231</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>97716359</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>116275570</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>259678468</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>152612406</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>345107924</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>230460594</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>62534590</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>57675796</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>61872149</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>57660949</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Investment securities (FVOCI - government securities, 100% UK/US/Belgium sovereign)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>146470054</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>151922722</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>107015424</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>82190414</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Property and equipment</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>3746354</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>3197915</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>2292269</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>691135</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Right-of-use leasehold property</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>9777616</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>10556149</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>11599109</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>616484</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Other assets</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>567044</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>440852</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>291795</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>898439</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Deferred tax asset</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>9284</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>12379</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>949586</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>2042560</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n">
-        <v>583445887</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>470783450</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>626844615</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>490836145</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Deposits by banks</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>329988520</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>217403953</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>344658275</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>291426385</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Deposits by customers</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>191532438</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>196877072</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>232269660</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>163962244</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Leasehold liability</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>10765913</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>11061158</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>11215172</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>704605</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Other liabilities</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>2832498</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>5875018</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>10338218</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>9598620</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Deferred tax liability</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>251139</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>175256</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>18912</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>54650</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>535370508</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>431392457</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>598500237</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>465746504</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Called up share capital</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>37000000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>11019326</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>2380687</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>-8026214</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>-11900852</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Fair value reserves</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n">
-        <v>56053</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>-9507</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Shareholders' funds (Total equity)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities and shareholders' funds</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n">
-        <v>583445887</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>470783450</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>626844615</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>490836145</v>
-      </c>
-    </row>
-    <row r="29" ht="260" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
-FY2023-FY2024 and 'Cash and cash equivalents' FY2021-FY2022 - same line, presentation relabelled;
-shown on separate rows above rather than merged, to match each year's own disclosed label.
-Investment securities note (Note 14, 'Investment securities'): all years' Annual Reports disclose the
-entire book as held at Fair Value through Other Comprehensive Income (FVOCI), with the Bank stating no
-financial assets are held at amortised cost or FVTPL, and as securities issued solely by government
-institutions (UK, US and, per the FY2024 Annual Report, Belgium) - FY2024: p.46; FY2022/FY2021: p.43
-of the FY2022 Annual Report (Note 14).
-Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
-each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
-FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
-standalone document - the same convention already used for the Cash Flow Statement sheet):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
-Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A29:F29"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Comprehensive Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As originally published in each year's own Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>26095367</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>24585386</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>12096324</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>3155907</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>-8140535</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>-5078320</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>-1902227</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>-780155</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Net interest income</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n">
-        <v>17954832</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>19507066</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>10194097</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>2375752</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Fees and commissions income</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>3222120</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>3544250</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>3569967</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>2462438</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Other operating income</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>4532851</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>4410543</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>3764651</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>2587967</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n">
-        <v>25709803</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>27461859</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>17528715</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>7426157</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Personnel expenses</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>-8202750</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>-8017084</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>-5831341</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>-5096462</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>-1370575</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>-1560012</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>-2176624</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>-1569766</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Other operating expenses</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>-4581738</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>-3959278</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-4458281</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>-10651872</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>-14155063</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>-13536374</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>-12466246</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>-17318100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n">
-        <v>180144</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>176822</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Rental income</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n">
-        <v>20786</v>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit impairment losses (charge)/reversal</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>-74019</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>12663</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-120728</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>-17516</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(Loss) before taxation</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n">
-        <v>11480721</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>13958934</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>5121885</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-9732637</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Taxation (charge)/credit</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>-2842082</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>-3552033</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>-1247247</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1402823</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(Loss) for the year</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>8638639</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>10406901</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>3874638</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-8329814</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income, net of corporation tax</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain/(loss) on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n">
-        <v>56053</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-6686</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Fair value (gain)/loss reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>-10306</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>629408</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>9507</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>-9507</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income/(loss) for the year, net of tax</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n">
-        <v>8684386</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>11046615</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>3254737</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>-8346007</v>
-      </c>
-    </row>
-    <row r="27" ht="200" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
-each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
-FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
-standalone document - the same convention already used for the Cash Flow Statement sheet):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
-Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Chronological roll-forward, oldest to newest. Equity reconciliation ladder confirmed: each year's own closing balance ties exactly to the next year's own opening balance and to that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fair value reserve</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Total equity</t>
+          <t>FY2021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Balance as at 1 January 2021</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>-3571038</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>6686</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>33435648</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>-8329814</v>
-      </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n">
-        <v>-8329814</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Net change in fair value</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n">
-        <v>-6686</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>-6686</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Net amount reclassified to P&amp;L</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n">
-        <v>-9507</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>-9507</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2021</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>-11900852</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>-9507</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>3874638</v>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n">
-        <v>3874638</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Fair value (loss) on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>-629408</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Net profit/(loss) reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n">
-        <v>9507</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>9507</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>-8026214</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>28344378</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>10406901</v>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n">
-        <v>10406901</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>10306</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Fair value loss reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n">
-        <v>629408</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>629408</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>2380687</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>39390993</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>8638639</v>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n">
-        <v>8638639</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n">
-        <v>56053</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>56053</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n">
-        <v>-10306</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>-10306</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>11019326</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>56053</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>48075379</v>
-      </c>
-    </row>
-    <row r="22" ht="200" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
-each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
-FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
-standalone document - the same convention already used for the Cash Flow Statement sheet):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
-Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:E22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="78" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Cash Flows</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As originally published in each year's own Annual Report (see DATA QUALITY note on a FY2021/FY2022 cash-equivalents basis discontinuity in the source citation below)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from operating activities</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Profit/(Loss) for the period before taxation</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>11480721</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>13958934</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>5121885</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>-9732637</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Amortisation of investment securities</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>-1476950</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>-1408658</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Interest income from investment securities</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>-7475529</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>-7178103</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>592042</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>517052</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>379244</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>570173</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Net (increase)/decrease in fair value of securities</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>-1192264</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses / allowances for credit impairment charge/(reversal)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>74019</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>-12663</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>120728</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Effective interest rate adjustment</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>-166166</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>-271506</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>-126000</v>
-      </c>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Lease finance charge</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>410509</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>415986</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>209082</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Provision for lease dilapidation</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>11240</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>10833</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Depreciation of leasehold right of use asset</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>778533</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1042960</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1797381</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>999594</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Operating cash flows before movement in working capital</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>5705369</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>8483493</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6025370</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>-10764152</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>(Increase)/decrease in loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>-44371958</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>54491422</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-6313430</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>29961133</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>(Increase)/decrease in loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>-4695033</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>4426364</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>-4402308</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>-6639736</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in other assets</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>-126192</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-149057</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>606644</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>52687</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in deposits by banks</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>112584567</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>-127254322</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>53231890</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>23544174</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in deposits by customers</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>-5344634</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>-35392588</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>68307416</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>9653264</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in other liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n">
-        <v>-1147659</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>-6957695</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>491009</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>6491319</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Changes in working capital (cumulative, incl. operating cash flows above)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n">
-        <v>62604460</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>-102352383</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>117946591</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>52298689</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Interest paid on leases</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n">
-        <v>-209082</v>
-      </c>
-      <c r="F23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Corporation tax (paid)/received</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>-4669205</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>25181</v>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) operating activities</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n">
-        <v>57935255</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>-102327202</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>117737509</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>52298689</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from investing activities</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Acquisition of investment securities</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n">
-        <v>-309552620</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>-322726031</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>-243814896</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>-160562399</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Sale and maturity of investment securities</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n">
-        <v>315933183</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>280019392</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>219731160</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>142726224</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Interest received from investment securities</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n">
-        <v>6597200</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>5617158</v>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Acquisition of property and equipment</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n">
-        <v>-1140481</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>-1422698</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>-1980378</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>-81236</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n">
-        <v>11837282</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>-38512179</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>-26064114</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>-17917411</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Repayment of lease</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n">
-        <v>-705754</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>-570000</v>
-      </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in lease liabilities</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n">
-        <v>-1892429</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>-1411693</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n">
-        <v>-705754</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>-570000</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>-1892429</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-1411693</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Net increase/(decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n">
-        <v>69066783</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>-141409381</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>89780966</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>32969585</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at the beginning of the year</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n">
-        <v>238999407</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>380408788</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>290627822</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>83305985</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at the end of the year</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n">
-        <v>308066190</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>238999407</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>380408788</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>116275570</v>
-      </c>
-    </row>
-    <row r="40" ht="230" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own Statement of Cash Flows, as originally
-published in each year's own Companies House-filed Annual Report and Financial Statements (not a later
-year's restated comparative, except where noted):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.26-27 (Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.26-27) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.25 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.24 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Asset Quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Loan book by maturity band and Expected Credit Loss (ECL) allowance, as originally published each year. The Bank does not disclose an IFRS 9 Stage 1/2/3 split anywhere in its Annual Report - only a single aggregate ECL figure per loan category - confirmed by reading Notes 12/13 and Note 23 (credit risk) in full each year; see source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Three months or less</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>207403713</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>144634176</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>335020113</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>218116770</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>One year or less but over three months</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>52375036</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>8003078</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>10166817</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>12416941</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>-100281</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>-24848</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>-79006</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>-73117</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Net loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n">
-        <v>259678468</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>152612406</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>345107924</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>230460594</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Three months or less</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>1784014</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1022971</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1040567</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>1416091</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>One year or less but over three months</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>5175504</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>4571746</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6260705</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>4406409</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Five years or less but over one year</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>17362794</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>15880590</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>15958829</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>16188919</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Over five years</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>38770629</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>36660770</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>39112659</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>35959033</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Less: Deferred Mortgage Arrangement Fees (EIR liability)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>-532746</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>-437081</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-389084</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>-307451</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n">
-        <v>-25605</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>-23200</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-111527</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>-2052</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Net loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n">
-        <v>62534590</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>57675796</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>61872149</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>57660949</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Derived ratios (not directly disclosed, computed for reference)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ECL coverage - loans and advances to customers (ECL / gross carrying amount)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="210" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604000</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
@@ -6610,13 +4007,3323 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Cash and money market funds</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>100662477</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>94365231</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>97716359</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>116275570</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>259678468</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>152612406</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>345107924</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>230460594</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>62534590</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>57675796</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>61872149</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>57660949</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Investment securities (FVOCI - government securities, 100% UK/US/Belgium sovereign)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>146470054</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>151922722</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>107015424</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>82190414</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>3746354</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3197915</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2292269</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>691135</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Right-of-use leasehold property</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>9777616</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>10556149</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>11599109</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>616484</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>567044</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>440852</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>291795</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>898439</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>9284</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>12379</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>949586</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2042560</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>583445887</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>470783450</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>626844615</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>490836145</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Deposits by banks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n">
+        <v>329988520</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>217403953</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>344658275</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>291426385</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Deposits by customers</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>191532438</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>196877072</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>232269660</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>163962244</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Leasehold liability</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>10765913</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>11061158</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>11215172</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>704605</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n">
+        <v>2832498</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>5875018</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>10338218</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>9598620</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>251139</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>175256</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>18912</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>54650</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>535370508</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>431392457</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>598500237</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>465746504</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>37000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>11019326</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>2380687</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-8026214</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-11900852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Fair value reserves</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Shareholders' funds (Total equity)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and shareholders' funds</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n">
+        <v>583445887</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>470783450</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>626844615</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>490836145</v>
+      </c>
+    </row>
+    <row r="29" ht="260" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
+FY2023-FY2024 and 'Cash and cash equivalents' FY2021-FY2022 - same line, presentation relabelled;
+shown on separate rows above rather than merged, to match each year's own disclosed label.
+Investment securities note (Note 14, 'Investment securities'): all years' Annual Reports disclose the
+entire book as held at Fair Value through Other Comprehensive Income (FVOCI), with the Bank stating no
+financial assets are held at amortised cost or FVTPL, and as securities issued solely by government
+institutions (UK, US and, per the FY2024 Annual Report, Belgium) - FY2024: p.46; FY2022/FY2021: p.43
+of the FY2022 Annual Report (Note 14).
+Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>26095367</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>24585386</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>12096324</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3155907</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>-8140535</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>-5078320</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-1902227</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>-780155</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>17954832</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>19507066</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>10194097</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2375752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Fees and commissions income</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>3222120</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>3544250</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3569967</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2462438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>4532851</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>4410543</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3764651</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>2587967</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>25709803</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>27461859</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>17528715</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7426157</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Personnel expenses</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>-8202750</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>-8017084</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>-5831341</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>-5096462</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>-1370575</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>-1560012</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>-2176624</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>-1569766</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>-4581738</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-3959278</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-4458281</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>-10651872</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>-14155063</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-13536374</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-12466246</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-17318100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>180144</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>176822</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Rental income</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>20786</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit impairment losses (charge)/reversal</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>-74019</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>12663</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-120728</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>-17516</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) before taxation</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>11480721</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>13958934</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5121885</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-9732637</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Taxation (charge)/credit</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>-2842082</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>-3552033</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-1247247</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1402823</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the year</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-8329814</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income, net of corporation tax</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain/(loss) on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-6686</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Fair value (gain)/loss reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>-10306</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>629408</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>9507</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n">
+        <v>8684386</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>11046615</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>3254737</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-8346007</v>
+      </c>
+    </row>
+    <row r="27" ht="200" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological roll-forward, oldest to newest. Equity reconciliation ladder confirmed: each year's own closing balance ties exactly to the next year's own opening balance and to that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Fair value reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>-3571038</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>6686</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>33435648</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Net change in fair value</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Net amount reclassified to P&amp;L</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11900852</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Fair value (loss) on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Net profit/(loss) reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n">
+        <v>9507</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9507</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-8026214</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>28344378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>10306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Fair value loss reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>629408</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>629408</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2380687</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>39390993</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>56053</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>11019326</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>48075379</v>
+      </c>
+    </row>
+    <row r="22" ht="200" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Cash Flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report (see DATA QUALITY note on a FY2021/FY2022 cash-equivalents basis discontinuity in the source citation below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the period before taxation</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>11480721</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>13958934</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5121885</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>-9732637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Amortisation of investment securities</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>-1476950</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>-1408658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Interest income from investment securities</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>-7475529</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-7178103</v>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>592042</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>517052</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>379244</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>570173</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Net (increase)/decrease in fair value of securities</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n">
+        <v>-1192264</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses / allowances for credit impairment charge/(reversal)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>74019</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>-12663</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>120728</v>
+      </c>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective interest rate adjustment</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>-166166</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>-271506</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-126000</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Lease finance charge</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>410509</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>415986</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>209082</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Provision for lease dilapidation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>11240</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>10833</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation of leasehold right of use asset</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>778533</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1042960</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1797381</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>999594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Operating cash flows before movement in working capital</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>5705369</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8483493</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6025370</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-10764152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>(Increase)/decrease in loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n">
+        <v>-44371958</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>54491422</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6313430</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>29961133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>(Increase)/decrease in loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>-4695033</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>4426364</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-4402308</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-6639736</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in other assets</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>-126192</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>-149057</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>606644</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>52687</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in deposits by banks</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n">
+        <v>112584567</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-127254322</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>53231890</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>23544174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in deposits by customers</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>-5344634</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>-35392588</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>68307416</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>9653264</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in other liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n">
+        <v>-1147659</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>-6957695</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>491009</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>6491319</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Changes in working capital (cumulative, incl. operating cash flows above)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n">
+        <v>62604460</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-102352383</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>117946591</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>52298689</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Interest paid on leases</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n">
+        <v>-209082</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Corporation tax (paid)/received</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>-4669205</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>25181</v>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n">
+        <v>57935255</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-102327202</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>117737509</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>52298689</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition of investment securities</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n">
+        <v>-309552620</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-322726031</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>-243814896</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>-160562399</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Sale and maturity of investment securities</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n">
+        <v>315933183</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>280019392</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>219731160</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>142726224</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Interest received from investment securities</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n">
+        <v>6597200</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>5617158</v>
+      </c>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition of property and equipment</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n">
+        <v>-1140481</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>-1422698</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>-1980378</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>-81236</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n">
+        <v>11837282</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>-38512179</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>-26064114</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-17917411</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Repayment of lease</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n">
+        <v>-705754</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in lease liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>-1411693</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n">
+        <v>-705754</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>-1411693</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Net increase/(decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n">
+        <v>69066783</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>-141409381</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>89780966</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>32969585</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the beginning of the year</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>290627822</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>83305985</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the end of the year</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n">
+        <v>308066190</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>116275570</v>
+      </c>
+    </row>
+    <row r="40" ht="230" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own Statement of Cash Flows, as originally
+published in each year's own Companies House-filed Annual Report and Financial Statements (not a later
+year's restated comparative, except where noted):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.26-27 (Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.26-27) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.25 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.24 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:F40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loan book by maturity band and Expected Credit Loss (ECL) allowance, as originally published each year. The Bank does not disclose an IFRS 9 Stage 1/2/3 split anywhere in its Annual Report - only a single aggregate ECL figure per loan category - confirmed by reading Notes 12/13 and Note 23 (credit risk) in full each year; see source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>207403713</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>144634176</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>335020113</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>218116770</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>52375036</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>8003078</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>10166817</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>12416941</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>-100281</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-24848</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-79006</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>-73117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>259678468</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>152612406</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>345107924</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>230460594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>1784014</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1022971</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1040567</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1416091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>5175504</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4571746</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6260705</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4406409</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Five years or less but over one year</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>17362794</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>15880590</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>15958829</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>16188919</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Over five years</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>38770629</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>36660770</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>39112659</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>35959033</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Less: Deferred Mortgage Arrangement Fees (EIR liability)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>-532746</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-437081</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-389084</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>-307451</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>-25605</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>-23200</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-111527</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>-2052</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>62534590</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>57675796</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>61872149</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>57660949</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios (not directly disclosed, computed for reference)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ECL coverage - loans and advances to customers (ECL / gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="210" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
+NOT been filed with Companies House - the company's own filing history shows its most recent accounts
+filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
+FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
+statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
+Statement, Asset Quality) is therefore genuinely blank for FY2025.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — KM1 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The Bank's own published key-metrics table, reproduced in GTBank's row order with its own labels and printed precision. GTBank prints the template WITHOUT row numbers and omits the SREP and additional-buffer blocks entirely, so neither is shown. Amounts in GBP '000, ratios as printed. Each year is as FIRST published in its own edition - this bank restates its comparatives materially, see the source note. FY2022 comes from the FY2023 edition because the FY2022 report predates the template; FY2021 appears in no KM1 at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available Own Funds (Amounts in GBP '000')</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ("CET1") capital  [printed as 37,000 in every year — see note]</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>37000</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>37000</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Total Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-Weighted Exposure Amount</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk-Weighted Exposure Amount</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>148821</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>157370</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>105275</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital Ratios (as a percentage of Risk-Weighted Exposure Amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Total Capital Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of Risk-Weighted Exposure Amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Capital Conversion Buffer (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Institution specific Countercyclical Capital Buffer (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Overall capital requirement (%)*</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>14.61%</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>14.67%</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>15.98%</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>CET1 available after the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>21.16%</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>12.28%</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>17.67%</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>4.70%</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>9.11%</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio ("LCR") — GBP '000 / %</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets (HQLA) (Weighted value) average of last 12mths</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>228692</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>188372</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>230533</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>176600</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Cash outflows - Total weighted value</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>410004</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>260717</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>199752</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>252991</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cash inflows -  Total weighted value</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>175251</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>218234</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>125298</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>189743</v>
+      </c>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (adjusted value)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>234753</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>42483</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>74454</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>63248</v>
+      </c>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>197%</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>309%</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>250%</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>274%</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio ("NSFR") — GBP '000 / %</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>198459</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>200729</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>194572</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>214036</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>94033</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>77347</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>62864</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>84527</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>211%</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>260%</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>310%</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>253%</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>* The asterisk is the Bank's own, on the "Overall capital requirement (%)" row of the FY2024 and FY2025 editions. Neither edition carries a matching footnote anywhere in the document: it is a dangling marker, reproduced rather than removed.</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="34" ht="420" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own key-metrics table, GBP '000 and percentages exactly as printed:
+FY2025: Pillar 3 Disclosure 2025, p.13-14, "Table 2: Key Metrics (GBP '000')", column 31st December 2025 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Pillar 3 Disclosure 2024, p.14, "Table 2: Key Metrics (GBP '000')", column 31st December 2024 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: Pillar 3 2023, p.13-14, "Key Metrics (GBP '000')", column 31st December 2023 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+FY2022: the comparative column of that same FY2023 edition, p.13-14 - see the edition note below - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+TABLE BREAKS ACROSS TWO PAGES in the FY2025 and FY2023 editions (capital, RWA, ratios and the start of the buffer block on the first page; the rest of the buffers, leverage, LCR and NSFR on the next), and sits whole on p.14 in the FY2024 edition. Page ranges above reflect that, so a later session verifying a citation does not stop at the first page and conclude the lower rows are missing.
+FY2021: no KM1 in any edition - blank.
+GTBANK PRINTS THE TEMPLATE UNNUMBERED AND ABRIDGED. The table carries the template's section headings and row labels in the template's order but no template row numbers at all, so none are shown here - supplying them from the PRA template would put words in the Bank's mouth. It also omits whole blocks the template defines: no "Additional own funds requirements based on SREP" section (no UK 7a-UK 7d), no UK 8a / UK 9a / 10 / UK 10a buffer rows, no UK 14a-14f leverage block, and no "Leverage ratio total exposure measure" amount row - only the ratio. Those absences are the Bank's own row set, not gaps in transcription. GTBank also drifts in capitalisation between editions ("Total Capital Ratio (%)" in FY2024/FY2025 against "Total capital ratio (%)" in FY2023, and likewise the buffer rows); the labels above follow the most recent edition.
+EDITION PER COLUMN, AND WHY IT MATTERS MORE HERE THAN USUAL. Every edition prints two columns, the reporting year and the prior year, and GTBank RESTATES its prior-year column materially. Taking each year from the edition in which it is the reporting year is therefore not a formality: the FY2024 edition restates FY2023 RWAs from 105,275 to 108,387 (3.0%), the CET1/Tier 1/Total ratio from 32.34% to 32.30%, the leverage ratio from 6.00% to 8.30%, HQLA from 230,533 to 197,710, the overall capital requirement from 14.67% to 14.07% and CET1-available from 17.67% to 18.23%. This sheet carries the as-first-published figures throughout. The restated FY2023 comparatives are recorded on their own labelled rows of the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio, Total RWAs and Leverage Ratio sheets, so neither version is lost and neither overwrites the other.
+FY2022 COMES FROM THE FY2023 EDITION BECAUSE ITS OWN EDITION HAS NO KM1. The FY2022 Pillar 3 report predates the template: it presents bespoke tables instead - "Table 3: Eligible Capital", "Table 4: Capital Adequacy Ratio (CAR) %" and "Table 5: CRR Leverage Ratio %" - with no template row labels or section headings, and the string NSFR does not occur in that document at all. Confirmed by reading the PDF rather than by a text search alone: its three embedded images (pages 1, 6 and 12) were listed and are a cover logo, the leverage-ratio table that extracts fine as text, and a risk-category diagram - there is no key-metrics table hidden as a bitmap. FY2021 appears inside no KM1 in any edition, so it is blank here; the FY2021 figures elsewhere in this workbook come from the FY2022 edition's bespoke tables.
+SOURCE DEFECT, REPRODUCED AND FLAGGED: THE CET1 CAPITAL ROW. GTBank prints "Common Equity Tier 1 ("CET1") capital  37,000" in every year of every edition - its paid-up share capital, unchanged since before this workbook's window - while the CET1 RATIO printed two rows below in the same column is struck on the Tier 1 / Total capital figure (FY2025: 54,604 / 148,821 = 36.69%, the printed ratio; 37,000 / 148,821 would be 24.86%). The Bank's own table is therefore internally inconsistent.
+A CONSTANT ACROSS FOUR YEARS IS NORMALLY A TRANSCRIPTION FAULT, SO THIS ONE WAS RE-INVESTIGATED FROM SCRATCH ON 16 SEPTEMBER 2026 BEFORE BEING ACCEPTED. Three candidate explanations were tested and all three were ruled out. (1) ROW MISALIGNMENT - ruled out by rendering each edition's page at 300 dpi and reading the ruled table cells directly rather than trusting `pdftotext`. That mattered: in the FY2025 edition the text layer emits the 2025 column of several rows on its own line ABOVE the row label (an artefact of vertical centring in taller cells), which is exactly what a column shift would look like. The rendered cell borders show it is not one - CET1 capital is a single-height row reading 37,000 | 37,000, while Tier 1 Capital and Total Capital read 54,604 | 48,075. The FY2024 and FY2023 editions have no vertical offset at all and print the same 37,000 in both of their columns. (2) A UNIT CHANGE BETWEEN EDITIONS - ruled out: all three editions head the table "Key Metrics (GBP '000')" and repeat "Amounts in GBP '000'" inside the header cell, so there is no unit break to mistake for a level shift. (3) THE TEMPLATE PRINTED TWICE ON TWO ENTITY BASES - ruled out: the key-metrics rows occur on exactly one page of each edition (FY2025 p.13, FY2024 p.14, FY2023 p.13), and the Bank states it has no subsidiaries in the UK or abroad, so there is no second basis to confuse.
+(4) A PARENT-LEVEL BLOCK READ BY MISTAKE - ruled out by the COLUMN HEADERS, which are the only thing that identifies an entity when a group and a subsidiary share a table. A constant that does not move while the entity's own capital moves is exactly what reading a parent column produces, so this was checked rather than assumed. GTBank's table is not of that shape: its two value columns are headed by DATES ("31st December 2025" and "31st December 2024"), not by entity names - there is no Group-beside-Individual split, no second table in an appendix, and the document is titled for Guaranty Trust Bank (UK) Limited throughout. Decisively, 37,000 is identified INSIDE THIS SAME DOCUMENT as the UK entity's own paid-up share capital by its section 7.1 build-up, which adds the UK entity's own P&amp;L reserve to it to reach the UK entity's own total capital. It is the right entity and the wrong LINE of that entity's build-up - a row-population error by the Bank, not a group-vs-subsidiary mix-up. The Nigerian parent (Guaranty Trust Bank Nigeria, under Guaranty Trust Holding Company) is outside the UK disclosure regime and publishes no UK KM1 for this subsidiary; nothing here is sourced from it.
+WHAT 37,000 ACTUALLY IS, from the Bank's own build-up. Each edition's section 7.1 "Table 4: Available Capital" derives capital as paid-up share capital 37,000 + Profit and Loss reserve 17,563 + fair value reserve 41 - intangibles nil = 54,604 "Total Capital Available" (FY2025 figures; FY2024 the same shape, 37,000 + 11,019 + 56 = 48,075), with Tier 2 and subordinated debt both nil, and the same section says in words that "Tier 1 Capital comprises paid-up share capital and the Profit &amp; Loss reserve less intangible assets". So the KM1 CET1 row has been populated with the FIRST LINE of that build-up instead of its total. That is the defect, and it is the Bank's, not this transcription's.
+BOTH FIGURES AND BOTH SOURCES, since the two sides of this workbook deliberately disagree. KM1 row = 37,000 in all four years, from the "Common Equity Tier 1 ("CET1") capital" row of Table 2 / "Key Metrics" in the FY2025 (p.13 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695), FY2024 (p.14 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481) and FY2023 (p.13 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289) editions. CET1 Capital sheet = 54,604,000 / 48,075,379 / 39,390,993 / 28,344,378, from each year's Annual Report Note 23.8(a) regulatory-capital table (https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0) and, for FY2025, from the FY2025 Pillar 3's own Table 4 "Total Capital Available" of 54,604 - the figure the ratios are actually struck on. The 37,000 is reproduced here unchanged because reproducing the template is the point of this sheet; NOTHING WAS EDITED ON EITHER SIDE TO MAKE THE TWO AGREE, and the four cross-check disagreements this raises in verify_workbook.py are expected and correct.
+ZERO GLYPHS. There are none: GTBank leaves no cell dashed or zeroed in this table. Every cell shown is a printed figure and every blank is a row or column the Bank did not print.
+LATEST-EDITION CHECK, 16 September 2026, against the Bank's own site rather than this script's citation list. gtbankuk.com publishes documents only from /about-gtbank-uk/our-company (the /investor-relations page renders no document links at all, in the HTML or in the sitemap). That page links exactly two reports: "GTBank-UK-Pillar-3-Disclosure-2025.pdf" and "GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf". The FY2025 Pillar 3 is the newest edition and is already cited here. Companies House (05969821) confirms the FY2025 Annual Report is not yet filed - the latest accounts are made up to 31 December 2024 - which is why FY2025 is Pillar 3-sourced throughout this workbook. Checked, none newer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6630,14 +7337,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£</t>
         </is>
       </c>
     </row>
@@ -6676,60 +7383,27 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>CET1 ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>CET1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -6804,8 +7478,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
+  <mergeCells count="1">
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6818,7 +7491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6832,14 +7505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
+          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -6878,34 +7551,60 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604000</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>CET1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CET1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -6981,8 +7680,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -1332,6 +1332,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2061,7 +2062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2082,7 +2083,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -2121,34 +2122,56 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
+          <t>Tier 1 capital - Annual Report Note 23.8(a), exact to the pound</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>54604000</v>
+        <v>54604</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>48075379</v>
+        <v>48075.379</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>39390993</v>
+        <v>39390.993</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>28344378</v>
+        <v>28344.378</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+        <v>25089.641</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.
+UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2224,8 +2247,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2439,7 +2462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2460,7 +2483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -2499,34 +2522,56 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total regulatory capital (unaudited)</t>
+          <t>Total regulatory capital (unaudited) - Annual Report Note 23.8(a), exact to the pound</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>54604000</v>
+        <v>54604</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>48075379</v>
+        <v>48075.379</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>39390993</v>
+        <v>39390.993</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>28344378</v>
+        <v>28344.378</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+        <v>25089.641</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total regulatory capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.
+UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2602,8 +2647,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3007,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3028,7 +3073,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5 - see the two SECTION blocks below and the sources note. FY2023: no reliable risk-type breakdown recoverable - see sources note.</t>
+          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5; FY2023 likewise derived but on the FY2024 edition's RESTATED FY2023 basis, in its own separate block - the Bank publishes no FY2023 risk-type split anywhere. Do not mix figures across the three blocks - see the sources note.</t>
         </is>
       </c>
     </row>
@@ -3216,8 +3261,76 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
     </row>
-    <row r="15" ht="280" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>FY2023 only — Pillar 1 capital requirement × 12.5 on the FY2024 edition's RESTATED FY2023 basis (108,387), NOT the as-first-published 105,275 — see sources note</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>75462.5</v>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>32762.5</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n">
+        <v>108387.5</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="20" ht="280" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
 FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
@@ -3225,6 +3338,8 @@
 FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
 FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
     On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
+    FY2023 ADDED 2026-09-18, ON EXACTLY THOSE TERMS. The paragraph above set the conditions and they are met here, so FY2023 now carries its own SEPARATE section rather than being merged into the FY2025/FY2024 derived block: the figures are the FY2024 edition's RESTATED FY2023 capital requirements x 12.5 (Credit 6,037 -&gt; 75,462.5; Market 13 -&gt; 162.5; Operational 2,621 -&gt; 32,762.5; total 108,387.5), every row label says 'restated basis', and the derived total is checked against that same edition's own restated FY2023 Total Risk-Weighted Exposure Amount of 108,387 - a gap of 0.5, pure GBP'000 rounding. It is deliberately NOT checked against the as-first-published 105,275, which remains the primary FY2023 row on the Total RWAs sheet and belongs to a different basis. The two sit in different sections of this sheet for that reason; a reader must not add a figure from the restated block to one from the as-disclosed block. Nothing about the underlying finding has changed: the Bank still publishes no FY2023 RWA split by risk type in any document, and every figure in this section is derived, never disclosed.
+(2026-09-18 FOURTH check, this time OUTSIDE the Pillar 3 series - the one place the three prior verifications had not looked. The Bank's own FY2023 ANNUAL REPORT AND FINANCIAL STATEMENTS (Companies House company 05969821, accounts made up to 31 December 2023, filed 25 June 2024) contains no risk-weighted asset amount at all, let alone a split: its note 23.8(a) 'Regulatory capital (unaudited)' prints only Tier 1 capital components and Total regulatory capital (39,390,993, against 28,344,378 for 2022), and its KPI table gives the CET1 ratio as a percentage (32.3%, 2022: 24.6%) with no denominator. The report is an IMAGE-ONLY SCAN (go-tiff2pdf, 71 pages, every page an image, zero-character text layer), so it was read by full-document OCR; positive control on the OCR output, 70 occurrences of 'capital' and 112 of 'ratio' against 0 of '105,275', 0 of '108,387' and 0 of any 'risk weighted assets' table. This closes the last plausible primary source: the FY2023 split does not exist in the Annual Report either.)
 (2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
 (2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
 (2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
@@ -3233,7 +3348,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3655,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3663,7 +3778,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3706,11 +3820,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -3738,7 +3847,6 @@
           <t>253%</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -3826,8 +3934,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4013,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4518,8 +4626,36 @@
         <v>490836145</v>
       </c>
     </row>
-    <row r="29" ht="260" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="31" ht="260" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
 FY2023-FY2024 and 'Cash and cash equivalents' FY2021-FY2022 - same line, presentation relabelled;
@@ -4543,12 +4679,36 @@
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
 conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -4572,7 +4732,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4584,7 +4744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -5047,8 +5207,36 @@
         <v>-8346007</v>
       </c>
     </row>
-    <row r="27" ht="200" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="29" ht="200" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
 each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
@@ -5064,12 +5252,36 @@
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
 conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -5093,7 +5305,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5448,12 +5660,36 @@
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
 conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -5489,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -6178,8 +6414,36 @@
         <v>116275570</v>
       </c>
     </row>
-    <row r="40" ht="230" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="42" ht="230" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own Statement of Cash Flows, as originally
 published in each year's own Companies House-filed Annual Report and Financial Statements (not a later
@@ -6193,12 +6457,36 @@
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
 conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -6222,7 +6510,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6234,7 +6522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -6575,8 +6863,36 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="210" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="22" ht="210" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
 Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
@@ -6584,12 +6900,36 @@
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
 conversion is required.
-FY2025 STATUS (re-verified 2026-09-15): the FY2025 statutory accounts (year ended 31 Dec 2025) still had
-NOT been filed with Companies House - the company's own filing history shows its most recent accounts
-filing is 'Full accounts made up to 31 December 2024', filed 6 May 2025, and Companies House records the
-FY2025 accounts as next due 30 September 2026 (i.e. not yet overdue, just not filed). Every statutory-
-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in Equity, Cash Flow
-Statement, Asset Quality) is therefore genuinely blank for FY2025.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -6613,7 +6953,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6625,7 +6965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -6633,7 +6973,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6676,11 +7015,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -6692,7 +7026,6 @@
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -6712,7 +7045,6 @@
       <c r="E5" s="7" t="n">
         <v>37000</v>
       </c>
-      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6732,7 +7064,6 @@
       <c r="E6" s="7" t="n">
         <v>28345</v>
       </c>
-      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6752,7 +7083,6 @@
       <c r="E7" s="7" t="n">
         <v>28345</v>
       </c>
-      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -6764,7 +7094,6 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6784,7 +7113,6 @@
       <c r="E9" s="7" t="n">
         <v>187034</v>
       </c>
-      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6796,7 +7124,6 @@
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -6824,7 +7151,6 @@
           <t>20.68%</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6852,7 +7178,6 @@
           <t>20.68%</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6880,7 +7205,6 @@
           <t>20.68%</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -6892,7 +7216,6 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -6920,7 +7243,6 @@
           <t>2.50%</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -6948,7 +7270,6 @@
           <t>1.00%</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -6976,7 +7297,6 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -7004,7 +7324,6 @@
           <t>15.98%</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -7032,7 +7351,6 @@
           <t>4.70%</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7044,7 +7362,6 @@
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -7072,7 +7389,6 @@
           <t>4.38%</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -7084,7 +7400,6 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -7104,7 +7419,6 @@
       <c r="E23" s="7" t="n">
         <v>176600</v>
       </c>
-      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -7124,7 +7438,6 @@
       <c r="E24" s="7" t="n">
         <v>252991</v>
       </c>
-      <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -7144,7 +7457,6 @@
       <c r="E25" s="7" t="n">
         <v>189743</v>
       </c>
-      <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -7164,7 +7476,6 @@
       <c r="E26" s="7" t="n">
         <v>63248</v>
       </c>
-      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -7192,7 +7503,6 @@
           <t>274%</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7204,7 +7514,6 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -7224,7 +7533,6 @@
       <c r="E29" s="7" t="n">
         <v>214036</v>
       </c>
-      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -7244,7 +7552,6 @@
       <c r="E30" s="7" t="n">
         <v>84527</v>
       </c>
-      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -7272,7 +7579,6 @@
           <t>253%</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -7284,7 +7590,6 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
     </row>
     <row r="34" ht="420" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -7311,7 +7616,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7323,7 +7628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7344,7 +7649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -7383,27 +7688,55 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
+          <t>Common Equity Tier 1 (CET1) capital - Annual Report Note 23.8(a), exact to the pound</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>54604000</v>
+        <v>54604</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>48075379</v>
+        <v>48075.379</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>39390993</v>
+        <v>39390.993</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>28344378</v>
+        <v>28344.378</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+        <v>25089.641</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -7478,7 +7811,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -4008,27 +4008,27 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in the FY2025 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in the FY2024 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in the FY2023 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3, which carries the FY2021 comparatives (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
     </row>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -115,7 +115,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="65" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Note: Pillar 3 ratios ARE disclosed for this entity (CET1/Tier 1/Total Capital ratio, leverage ratio, LCR, and NSFR from FY2023) - see those individual metric sheets; only MREL is never numerically disclosed. They are not repeated in the ratio block above. The statutory-statement figures above are blank for FY2025 because no FY2025 Annual Report has been filed with Companies House yet (next due 30 Sep 2026), even though the FY2025 Pillar 3 disclosure has been published - so the Pillar 3 sheets do carry a full FY2025 column. Figures above are duplicated from the Cash Flow Statement sheet for at-a-glance trend viewing; see that sheet's own source citation, including a flagged FY2021/FY2022 basis discontinuity in the cash-equivalents figures.</t>
@@ -2062,7 +2062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="117" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.
@@ -2170,7 +2170,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="170" customHeight="1">
+    <row r="8" ht="390" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
@@ -2199,7 +2199,1824 @@
     is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
     while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
     section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="390" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Total regulatory capital (unaudited) - Annual Report Note 23.8(a), exact to the pound</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075.379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390.993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344.378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089.641</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total regulatory capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="117" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.
+UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="390" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Total Capital Ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="390" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>148821</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>157370</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>105275</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n">
+        <v>108387</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="390" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5; FY2023 likewise derived but on the FY2024 edition's RESTATED FY2023 basis, in its own separate block - the Bank publishes no FY2023 risk-type split anywhere. Do not mix figures across the three blocks - see the sources note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>166793</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>77962</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>20026</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>22148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>98212.5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>113012.5</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>50337.5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>44187.5</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>148825</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>157375</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>FY2023 only — Pillar 1 capital requirement × 12.5 on the FY2024 edition's RESTATED FY2023 basis (108,387), NOT the as-first-published 105,275 — see sources note</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>75462.5</v>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>32762.5</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n">
+        <v>108387.5</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="20" ht="390" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
+FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
+    FY2023 ADDED 2026-09-18, ON EXACTLY THOSE TERMS. The paragraph above set the conditions and they are met here, so FY2023 now carries its own SEPARATE section rather than being merged into the FY2025/FY2024 derived block: the figures are the FY2024 edition's RESTATED FY2023 capital requirements x 12.5 (Credit 6,037 -&gt; 75,462.5; Market 13 -&gt; 162.5; Operational 2,621 -&gt; 32,762.5; total 108,387.5), every row label says 'restated basis', and the derived total is checked against that same edition's own restated FY2023 Total Risk-Weighted Exposure Amount of 108,387 - a gap of 0.5, pure GBP'000 rounding. It is deliberately NOT checked against the as-first-published 105,275, which remains the primary FY2023 row on the Total RWAs sheet and belongs to a different basis. The two sit in different sections of this sheet for that reason; a reader must not add a figure from the restated block to one from the as-disclosed block. Nothing about the underlying finding has changed: the Bank still publishes no FY2023 RWA split by risk type in any document, and every figure in this section is derived, never disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="280" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+(2026-09-18 FOURTH check, this time OUTSIDE the Pillar 3 series - the one place the three prior verifications had not looked. The Bank's own FY2023 ANNUAL REPORT AND FINANCIAL STATEMENTS (Companies House company 05969821, accounts made up to 31 December 2023, filed 25 June 2024) contains no risk-weighted asset amount at all, let alone a split: its note 23.8(a) 'Regulatory capital (unaudited)' prints only Tier 1 capital components and Total regulatory capital (39,390,993, against 28,344,378 for 2022), and its KPI table gives the CET1 ratio as a percentage (32.3%, 2022: 24.6%) with no denominator. The report is an IMAGE-ONLY SCAN (go-tiff2pdf, 71 pages, every page an image, zero-character text layer), so it was read by full-document OCR; positive control on the OCR output, 70 occurrences of 'capital' and 112 of 'ratio' against 0 of '105,275', 0 of '108,387' and 0 of any 'risk weighted assets' table. This closes the last plausible primary source: the FY2023 split does not exist in the Annual Report either.)
+(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
+(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
+(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Leverage Ratio (as first published in each year's own Pillar 3 report) - the Bank's Key Metrics row is LABELLED 'excluding claims on central banks' but prints the same value as its own narrative ratio in every edition, i.e. no exclusion is actually made; see note</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>9.11%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>8.29%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>8.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="299" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
+  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
+  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
+  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
+FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 6 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (6 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. No edition contained either. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="390" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="403" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="182" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>197%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>309%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>250%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>274%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>356%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
+DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
+By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="390" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="403" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="182" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>211%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>260%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>310%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>253%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="91" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2022 (253%) was added 2026-09-15. The FY2022 Pillar 3 report itself never mentions NSFR at all (the string does not occur in the document), but the FY2023 report's Key Metrics table carries a full FY2022 comparative column for it - Total available stable funding 214,036 / Total required stable funding 84,527 (GBP'000), printed ratio 253%. That is the Bank's own figure for its own entity, on the same basis as every other year on this sheet, so it is transcribed here; the same comparative-column convention is already used for FY2021 elsewhere in this workbook.
+FY2021 remains blank: no NSFR is disclosed for it in any reviewed edition, and nothing is substituted from another entity.
+Unlike the LCR sheet, the NSFR components reconcile to the printed ratio exactly in every disclosed year: FY2025 198,459 / 94,033 = 211%; FY2024 200,729 / 77,347 = 260%; FY2023 194,572 / 62,864 = 310%; FY2022 214,036 / 84,527 = 253% (GBP'000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="390" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="403" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
     Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
     Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
     ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
@@ -2227,7 +4044,14 @@
   Operational risk MCR                               2,643                         2,621
   Pillar 1 requirement                               8,368                         8,671
   HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="195" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
 capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
@@ -2246,24 +4070,26 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2274,16 +4100,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2320,60 +4142,37 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 ratio (as first published)</t>
+          <t>MREL Ratio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>36.69%</t>
+          <t>Not published – no MREL figure in the FY2025 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>26.89%</t>
+          <t>Not published – no MREL figure in the FY2024 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>32.34%</t>
+          <t>Not published – no MREL figure in the FY2023 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>20.68%</t>
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3, which carries the FY2021 comparatives (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="390" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -2401,8 +4200,15 @@
     is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
     while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
     section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="403" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
     Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
     ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
     same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
@@ -2430,7 +4236,14 @@
   Pillar 1 requirement                               8,368                         8,671
   HQLA (12m average, weighted)                     230,533                       197,710
   Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="182" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
 capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
 to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
@@ -2448,1668 +4261,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Total regulatory capital (unaudited) - Annual Report Note 23.8(a), exact to the pound</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075.379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390.993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344.378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089.641</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Total regulatory capital - as printed in the Pillar 3 Key Metrics table</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>48075</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>39391</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>28345</v>
-      </c>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.
-UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
-ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Total Capital Ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>148821</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>157370</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>105275</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>100287</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n">
-        <v>108387</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5; FY2023 likewise derived but on the FY2024 edition's RESTATED FY2023 basis, in its own separate block - the Bank publishes no FY2023 risk-type split anywhere. Do not mix figures across the three blocks - see the sources note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£'000)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n">
-        <v>166793</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>77962</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>20026</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>22148</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n">
-        <v>215</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>100287</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>98212.5</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>113012.5</v>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>275</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>50337.5</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>44187.5</v>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>148825</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>157375</v>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>FY2023 only — Pillar 1 capital requirement × 12.5 on the FY2024 edition's RESTATED FY2023 basis (108,387), NOT the as-first-published 105,275 — see sources note</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n">
-        <v>75462.5</v>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n">
-        <v>32762.5</v>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n">
-        <v>108387.5</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="20" ht="280" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
-FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
-    FY2023 ADDED 2026-09-18, ON EXACTLY THOSE TERMS. The paragraph above set the conditions and they are met here, so FY2023 now carries its own SEPARATE section rather than being merged into the FY2025/FY2024 derived block: the figures are the FY2024 edition's RESTATED FY2023 capital requirements x 12.5 (Credit 6,037 -&gt; 75,462.5; Market 13 -&gt; 162.5; Operational 2,621 -&gt; 32,762.5; total 108,387.5), every row label says 'restated basis', and the derived total is checked against that same edition's own restated FY2023 Total Risk-Weighted Exposure Amount of 108,387 - a gap of 0.5, pure GBP'000 rounding. It is deliberately NOT checked against the as-first-published 105,275, which remains the primary FY2023 row on the Total RWAs sheet and belongs to a different basis. The two sit in different sections of this sheet for that reason; a reader must not add a figure from the restated block to one from the as-disclosed block. Nothing about the underlying finding has changed: the Bank still publishes no FY2023 RWA split by risk type in any document, and every figure in this section is derived, never disclosed.
-(2026-09-18 FOURTH check, this time OUTSIDE the Pillar 3 series - the one place the three prior verifications had not looked. The Bank's own FY2023 ANNUAL REPORT AND FINANCIAL STATEMENTS (Companies House company 05969821, accounts made up to 31 December 2023, filed 25 June 2024) contains no risk-weighted asset amount at all, let alone a split: its note 23.8(a) 'Regulatory capital (unaudited)' prints only Tier 1 capital components and Total regulatory capital (39,390,993, against 28,344,378 for 2022), and its KPI table gives the CET1 ratio as a percentage (32.3%, 2022: 24.6%) with no denominator. The report is an IMAGE-ONLY SCAN (go-tiff2pdf, 71 pages, every page an image, zero-character text layer), so it was read by full-document OCR; positive control on the OCR output, 70 occurrences of 'capital' and 112 of 'ratio' against 0 of '105,275', 0 of '108,387' and 0 of any 'risk weighted assets' table. This closes the last plausible primary source: the FY2023 split does not exist in the Annual Report either.)
-(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
-(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
-(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Leverage Ratio (as first published in each year's own Pillar 3 report)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>9.11%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>8.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>4.38%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>8.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
-  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
-  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
-  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
-FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>197%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>309%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>250%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>274%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>356%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
-DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
-By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — NSFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Net Stable Funding Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>211%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>260%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>310%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>253%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: FY2022 (253%) was added 2026-09-15. The FY2022 Pillar 3 report itself never mentions NSFR at all (the string does not occur in the document), but the FY2023 report's Key Metrics table carries a full FY2022 comparative column for it - Total available stable funding 214,036 / Total required stable funding 84,527 (GBP'000), printed ratio 253%. That is the Bank's own figure for its own entity, on the same basis as every other year on this sheet, so it is transcribed here; the same comparative-column convention is already used for FY2021 elsewhere in this workbook.
-FY2021 remains blank: no NSFR is disclosed for it in any reviewed edition, and nothing is substituted from another entity.
-Unlike the LCR sheet, the NSFR components reconcile to the printed ratio exactly in every disclosed year: FY2025 198,459 / 94,033 = 211%; FY2024 200,729 / 77,347 = 260%; FY2023 194,572 / 62,864 = 310%; FY2022 214,036 / 84,527 = 253% (GBP'000).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A7:E7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2025 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2024 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2023 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3, which carries the FY2021 comparatives (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4121,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4654,7 +4809,7 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
     </row>
-    <row r="31" ht="260" customHeight="1">
+    <row r="31" ht="377" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>The Bank's own Statement of financial position labels the cash line 'Cash and money market funds'
@@ -4678,7 +4833,14 @@
 subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
 Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
 (Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
+conversion is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="403" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
 still had NOT been published anywhere. Two independent routes were checked on that date and both are
 negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
@@ -4708,7 +4870,14 @@
 ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
 and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
 document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
-guessed into place.
+guessed into place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="273" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
 2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
 https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
@@ -4731,8 +4900,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4744,7 +4915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -5235,7 +5406,7 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
     </row>
-    <row r="29" ht="200" customHeight="1">
+    <row r="29" ht="390" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
@@ -5261,6 +5432,1702 @@
 https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
 'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
 - and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="403" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="200" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological roll-forward, oldest to newest. Equity reconciliation ladder confirmed: each year's own closing balance ties exactly to the next year's own opening balance and to that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Fair value reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>-3571038</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>6686</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>33435648</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>-8329814</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Net change in fair value</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-6686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Net amount reclassified to P&amp;L</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-9507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11900852</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25089641</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n">
+        <v>3874638</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Fair value (loss) on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>-629408</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Net profit/(loss) reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n">
+        <v>9507</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9507</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-8026214</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-629408</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>28344378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>10406901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>10306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Fair value loss reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>629408</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>629408</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2380687</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10306</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>39390993</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n">
+        <v>8638639</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain on FVOCI investment securities, net of tax</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>56053</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Fair value gain reclassified to profit or loss</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-10306</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>11019326</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>56053</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>48075379</v>
+      </c>
+    </row>
+    <row r="22" ht="390" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
+each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
+FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
+standalone document - the same convention already used for the Cash Flow Statement sheet):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
+Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="403" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="200" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Statement of Cash Flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As originally published in each year's own Annual Report (see DATA QUALITY note on a FY2021/FY2022 cash-equivalents basis discontinuity in the source citation below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the period before taxation</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>11480721</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>13958934</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5121885</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>-9732637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Amortisation of investment securities</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>-1476950</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>-1408658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Interest income from investment securities</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>-7475529</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-7178103</v>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>592042</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>517052</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>379244</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>570173</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Net (increase)/decrease in fair value of securities</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n">
+        <v>-1192264</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses / allowances for credit impairment charge/(reversal)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>74019</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>-12663</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>120728</v>
+      </c>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective interest rate adjustment</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>-166166</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>-271506</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-126000</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Lease finance charge</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>410509</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>415986</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>209082</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Provision for lease dilapidation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>11240</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>10833</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation of leasehold right of use asset</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>778533</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1042960</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1797381</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>999594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Operating cash flows before movement in working capital</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>5705369</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8483493</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6025370</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-10764152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>(Increase)/decrease in loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n">
+        <v>-44371958</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>54491422</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6313430</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>29961133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>(Increase)/decrease in loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>-4695033</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>4426364</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-4402308</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-6639736</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in other assets</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>-126192</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>-149057</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>606644</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>52687</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in deposits by banks</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n">
+        <v>112584567</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-127254322</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>53231890</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>23544174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in deposits by customers</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>-5344634</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>-35392588</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>68307416</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>9653264</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in other liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n">
+        <v>-1147659</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>-6957695</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>491009</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>6491319</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Changes in working capital (cumulative, incl. operating cash flows above)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n">
+        <v>62604460</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-102352383</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>117946591</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>52298689</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Interest paid on leases</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n">
+        <v>-209082</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Corporation tax (paid)/received</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>-4669205</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>25181</v>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n">
+        <v>57935255</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-102327202</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>117737509</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>52298689</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition of investment securities</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n">
+        <v>-309552620</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-322726031</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>-243814896</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>-160562399</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Sale and maturity of investment securities</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n">
+        <v>315933183</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>280019392</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>219731160</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>142726224</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Interest received from investment securities</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n">
+        <v>6597200</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>5617158</v>
+      </c>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition of property and equipment</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n">
+        <v>-1140481</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>-1422698</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>-1980378</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>-81236</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n">
+        <v>11837282</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>-38512179</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>-26064114</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-17917411</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Repayment of lease</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n">
+        <v>-705754</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Increase/(decrease) in lease liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>-1411693</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n">
+        <v>-705754</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-570000</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-1892429</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>-1411693</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Net increase/(decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n">
+        <v>69066783</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>-141409381</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>89780966</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>32969585</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the beginning of the year</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>290627822</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>83305985</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the end of the year</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n">
+        <v>308066190</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>238999407</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>380408788</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>116275570</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="42" ht="390" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own Statement of Cash Flows, as originally
+published in each year's own Companies House-filed Annual Report and Financial Statements (not a later
+year's restated comparative, except where noted):
+FY2024: Annual Report for the year ended 31 Dec 2024, p.26-27 (Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.26-27) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Annual Report for the year ended 31 Dec 2022, p.25 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Annual Report for the year ended 31 Dec 2021, p.24 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
+Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
+Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
+distinct from not reachable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="403" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
+directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
+Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
+Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
+December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
+operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
+8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
+precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
+the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
+ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
+the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
+expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
+ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
+and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
+document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
+guessed into place.
+The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
+2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
+https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
+from it - see the Pillar 3 sheets' own source citation.
+DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
+'cash and cash equivalents for 2021 have been re-presented to include money market placements with
+maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
+from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
+GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
+Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
+GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="230" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+traced or resolved. Per this project's convention, each year below uses its own originally-published
+figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
+is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
+cash-bridge gap elsewhere in this project.
+Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
+(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
+source rounding artifact, not corrected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A46:F46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loan book by maturity band and Expected Credit Loss (ECL) allowance, as originally published each year. The Bank does not disclose an IFRS 9 Stage 1/2/3 split anywhere in its Annual Report - only a single aggregate ECL figure per loan category - confirmed by reading Notes 12/13 and Note 23 (credit risk) in full each year; see source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
+        <v>207403713</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>144634176</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>335020113</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>218116770</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>52375036</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>8003078</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>10166817</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>12416941</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>-100281</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-24848</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-79006</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>-73117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>259678468</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>152612406</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>345107924</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>230460594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Three months or less</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>1784014</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1022971</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1040567</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1416091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>One year or less but over three months</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>5175504</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>4571746</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6260705</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4406409</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Five years or less but over one year</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n">
+        <v>17362794</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>15880590</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>15958829</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>16188919</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Over five years</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>38770629</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>36660770</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>39112659</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>35959033</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Less: Deferred Mortgage Arrangement Fees (EIR liability)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>-532746</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-437081</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-389084</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>-307451</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>-25605</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>-23200</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-111527</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>-2052</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>62534590</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>57675796</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>61872149</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>57660949</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios (not directly disclosed, computed for reference)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ECL coverage - loans and advances to customers (ECL / gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 status</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>FY2025 column</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="22" ht="390" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
+Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
+subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
+Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
+(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
+conversion is required.
+FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
+still had NOT been published anywhere. Two independent routes were checked on that date and both are
+negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
+recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
+9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
+30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
+https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
+'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
+- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
 Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
 Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
 distinct from not reachable.
@@ -5270,7 +7137,14 @@
 Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
 December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
 operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
-6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
+6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="409" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
 8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
 precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
@@ -5304,1655 +7178,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A29:F29"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Changes in Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Chronological roll-forward, oldest to newest. Equity reconciliation ladder confirmed: each year's own closing balance ties exactly to the next year's own opening balance and to that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fair value reserve</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Balance as at 1 January 2021</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>-3571038</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>6686</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>33435648</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>-8329814</v>
-      </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n">
-        <v>-8329814</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Net change in fair value</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n">
-        <v>-6686</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>-6686</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Net amount reclassified to P&amp;L</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n">
-        <v>-9507</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>-9507</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2021</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>-11900852</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>-9507</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>25089641</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>3874638</v>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n">
-        <v>3874638</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Fair value (loss) on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>-629408</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Net profit/(loss) reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n">
-        <v>9507</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>9507</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>-8026214</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>-629408</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>28344378</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>10406901</v>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n">
-        <v>10406901</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>10306</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Fair value loss reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n">
-        <v>629408</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>629408</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>2380687</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>10306</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>39390993</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>8638639</v>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n">
-        <v>8638639</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain on FVOCI investment securities, net of tax</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n">
-        <v>56053</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>56053</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Fair value gain reclassified to profit or loss</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n">
-        <v>-10306</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>-10306</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>11019326</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>56053</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>48075379</v>
-      </c>
-    </row>
-    <row r="22" ht="200" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own statements, as originally published in
-each year's own Companies House-filed Annual Report and Financial Statements (FY2023 sourced from the
-FY2024 Annual Report's own FY2023 comparative column, since no separate FY2023 filing exists as a
-standalone document - the same convention already used for the Cash Flow Statement sheet):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.23-25 (Statement of comprehensive income,
-Statement of financial position, Statement of changes in equity) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.23-25) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.22-24 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.21-23 - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
-still had NOT been published anywhere. Two independent routes were checked on that date and both are
-negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
-recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
-9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
-30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
-https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
-'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
-- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
-Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
-Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
-distinct from not reachable.
-THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
-directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
-Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
-Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
-December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
-operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
-6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
-Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
-8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
-precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
-the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
-ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
-the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
-expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
-ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
-and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
-document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
-guessed into place.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:E22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="78" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Statement of Cash Flows</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As originally published in each year's own Annual Report (see DATA QUALITY note on a FY2021/FY2022 cash-equivalents basis discontinuity in the source citation below)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from operating activities</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Profit/(Loss) for the period before taxation</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>11480721</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>13958934</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>5121885</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>-9732637</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Amortisation of investment securities</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>-1476950</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>-1408658</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Interest income from investment securities</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>-7475529</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>-7178103</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>592042</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>517052</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>379244</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>570173</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Net (increase)/decrease in fair value of securities</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>-1192264</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses / allowances for credit impairment charge/(reversal)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>74019</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>-12663</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>120728</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Effective interest rate adjustment</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>-166166</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>-271506</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>-126000</v>
-      </c>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Lease finance charge</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>410509</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>415986</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>209082</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Provision for lease dilapidation</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>11240</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>10833</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Depreciation of leasehold right of use asset</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>778533</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1042960</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1797381</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>999594</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Operating cash flows before movement in working capital</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>5705369</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>8483493</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6025370</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>-10764152</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>(Increase)/decrease in loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>-44371958</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>54491422</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-6313430</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>29961133</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>(Increase)/decrease in loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>-4695033</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>4426364</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>-4402308</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>-6639736</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in other assets</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>-126192</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-149057</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>606644</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>52687</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in deposits by banks</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>112584567</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>-127254322</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>53231890</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>23544174</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in deposits by customers</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>-5344634</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>-35392588</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>68307416</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>9653264</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in other liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n">
-        <v>-1147659</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>-6957695</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>491009</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>6491319</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Changes in working capital (cumulative, incl. operating cash flows above)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n">
-        <v>62604460</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>-102352383</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>117946591</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>52298689</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Interest paid on leases</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n">
-        <v>-209082</v>
-      </c>
-      <c r="F23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Corporation tax (paid)/received</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>-4669205</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>25181</v>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) operating activities</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n">
-        <v>57935255</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>-102327202</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>117737509</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>52298689</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from investing activities</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Acquisition of investment securities</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n">
-        <v>-309552620</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>-322726031</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>-243814896</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>-160562399</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Sale and maturity of investment securities</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n">
-        <v>315933183</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>280019392</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>219731160</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>142726224</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Interest received from investment securities</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n">
-        <v>6597200</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>5617158</v>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Acquisition of property and equipment</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n">
-        <v>-1140481</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>-1422698</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>-1980378</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>-81236</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n">
-        <v>11837282</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>-38512179</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>-26064114</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>-17917411</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Repayment of lease</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n">
-        <v>-705754</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>-570000</v>
-      </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Increase/(decrease) in lease liabilities</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n">
-        <v>-1892429</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>-1411693</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flow from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n">
-        <v>-705754</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>-570000</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>-1892429</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-1411693</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Net increase/(decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n">
-        <v>69066783</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>-141409381</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>89780966</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>32969585</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at the beginning of the year</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n">
-        <v>238999407</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>380408788</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>290627822</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>83305985</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at the end of the year</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n">
-        <v>308066190</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>238999407</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>380408788</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>116275570</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>FY2025 status</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>FY2025 column</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-    </row>
-    <row r="42" ht="230" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Sources - all figures are Guaranty Trust Bank (UK) Limited's own Statement of Cash Flows, as originally
-published in each year's own Companies House-filed Annual Report and Financial Statements (not a later
-year's restated comparative, except where noted):
-FY2024: Annual Report for the year ended 31 Dec 2024, p.26-27 (Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: as above (FY2024 Annual Report's own FY2023 comparative column, p.26-27) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022: Annual Report for the year ended 31 Dec 2022, p.25 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQwNjA2NDkyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2021: Annual Report for the year ended 31 Dec 2021, p.24 (Statement of cash flows) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzM3MzI3NjAyMmFkaXF6a2N4/document?format=pdf&amp;download=0
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
-still had NOT been published anywhere. Two independent routes were checked on that date and both are
-negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
-recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
-9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
-30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
-https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
-'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
-- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
-Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
-Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
-distinct from not reachable.
-THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
-directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
-Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
-Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
-December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
-operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
-6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
-Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
-8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
-precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
-the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
-ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
-the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
-expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
-ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
-and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
-document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
-guessed into place.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A42:F42"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — Asset Quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Loan book by maturity band and Expected Credit Loss (ECL) allowance, as originally published each year. The Bank does not disclose an IFRS 9 Stage 1/2/3 split anywhere in its Annual Report - only a single aggregate ECL figure per loan category - confirmed by reading Notes 12/13 and Note 23 (credit risk) in full each year; see source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Three months or less</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>207403713</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>144634176</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>335020113</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>218116770</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>One year or less but over three months</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>52375036</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>8003078</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>10166817</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>12416941</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>-100281</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>-24848</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>-79006</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>-73117</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Net loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n">
-        <v>259678468</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>152612406</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>345107924</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>230460594</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Three months or less</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>1784014</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1022971</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1040567</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>1416091</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>One year or less but over three months</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>5175504</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>4571746</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6260705</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>4406409</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Five years or less but over one year</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>17362794</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>15880590</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>15958829</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>16188919</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Over five years</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>38770629</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>36660770</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>39112659</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>35959033</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Less: Deferred Mortgage Arrangement Fees (EIR liability)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>-532746</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>-437081</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-389084</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>-307451</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Expected credit losses</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n">
-        <v>-25605</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>-23200</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-111527</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>-2052</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Net loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n">
-        <v>62534590</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>57675796</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>61872149</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>57660949</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Derived ratios (not directly disclosed, computed for reference)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ECL coverage - loans and advances to customers (ECL / gross carrying amount)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>FY2025 status</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>FY2025 column</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Not published yet - FY2025 accounts audited (Forvis Mazars) but not public; Companies House 05969821 next due 30 Sep 2026, not overdue. Checked 2026-09-18.</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-    </row>
-    <row r="22" ht="210" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Notes 12 (Loans and advances to banks) and 13 (Loans and advances to customers) of each year's own Annual Report (same documents as the Balance Sheet sheet above); FY2023 sourced from the FY2024 Annual Report's own FY2023 comparative column. Each year's own Annual Report states 'All loans and advances to banks were performing' and loans and advances to customers were 'performing or adequately collateralised' - no non-performing loan balance is disclosed for any year. The ECL coverage ratio row is calculated (ECL / (gross carrying amount before ECL)), not a figure the Bank itself publishes - shown for reference only.
-Guaranty Trust Bank (UK) Limited (FRN 466611, Companies House 05969821) is a wholly-owned UK
-subsidiary of Guaranty Trust Bank Limited ('GTBank Nigeria'), itself wholly owned by Guaranty Trust
-Holding Company Plc (GTCO). Unlike several other Nigerian-bank-owned UK subsidiaries in this project
-(Zenith Bank UK, UBA UK, FCMB UK, FidBank UK), this entity reports in GBP throughout - no FX
-conversion is required.
-FY2025 STATUS (re-verified 2026-09-18, unchanged): the FY2025 statutory accounts (year ended 31 Dec 2025)
-still had NOT been published anywhere. Two independent routes were checked on that date and both are
-negative. (1) Companies House filing history for 05969821 lists exactly five accounts filings, the most
-recent being 'Full accounts made up to 31 December 2024', filed 6 May 2025 (the others 25 Jun 2024,
-9 Jan 2024, 22 Mar 2023 and 1 Mar 2022); Companies House records the FY2025 accounts as next due
-30 September 2026, i.e. not yet overdue, just not filed. (2) The Bank's own document page,
-https://www.gtbankuk.com/about-gtbank-uk/our-company, links exactly two financial documents - the
-'GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf' and the 'GTBank-UK-Pillar-3-Disclosure-2025.pdf'
-- and its own in-page anchor is still literally #section-gt-bank-uk-annual-report-and-financial-statement-2024.
-Every statutory-statement sheet in this workbook (Balance Sheet, Profit &amp; Loss, Statement of Changes in
-Equity, Cash Flow Statement, Asset Quality) is therefore genuinely blank for FY2025 - NOT PUBLISHED, as
-distinct from not reachable.
-THE FY2025 ACCOUNTS DO EXIST AND ARE AUDITED, they are simply not public. The FY2025 Pillar 3 says so
-directly (section 5.1): its Table 1 'Financial Performance (GBP 000)' figures are 'as quoted in the Bank's
-Financial Statements (Accounts) and, as such have been audited by the Bank's external auditors, Forvis
-Mazars LLP', referring the reader to 'the Annual Report and Financial Statements (the Accounts) FYE 31st
-December 2025'. That table prints six FY2025 aggregates, in GBP'000: net interest income 16,811,
-operating income 24,325, profit before taxation 9,058, taxation charge (2,304), profit after taxation
-6,754, total comprehensive income 6,738. They are recorded here rather than written into the Profit &amp;
-Loss sheet, DELIBERATELY: that sheet is denominated in pounds to the penny (FY2024 profit after tax is
-8,638,639, not 8,639,000), so posting a GBP'000-rounded aggregate into it would invent three digits of
-precision, and the six lines cover only 6 of the sheet's 20 rows in any case. When the accounts are filed
-the FY2025 column should be transcribed from them in full, and these six figures used as a cross-check.
-ASSET QUALITY, likewise not filled from the Pillar 3, for a different and sharper reason. Section 8.8 of
-the FY2025 Pillar 3 states the Bank 'had allocated GBP198,514 (31st December 2024: GBP100,281) for
-expected losses under IFRS 9'. The FY2024 comparative in that sentence, 100,281, is NOT the FY2024 total
-ECL allowance in this workbook's Asset Quality sheet (100,281 + 25,605 = 125,886); it equals the loans-
-and-advances-to-BANKS ECL alone. The scope of the FY2025 figure is therefore unresolved on the face of the
-document, and it is not attributable to any single row of that sheet. It is recorded here instead of being
-guessed into place.
-The Pillar 3 sheets are NOT blank for FY2025: the Bank published its own standalone 'Pillar 3 Disclosure
-2025' (as at 31 December 2025, PDF created 23 July 2026, linked from its own site at
-https://www.gtbankuk.com/about-gtbank-uk/our-company), and every Pillar 3 metric below is transcribed
-from it - see the Pillar 3 sheets' own source citation.
-DATA QUALITY NOTE - cash-equivalents basis discontinuity: the FY2022 Annual Report states that
-'cash and cash equivalents for 2021 have been re-presented to include money market placements with
-maturity of less than 3 months', quantifying the impact as an increase in the FY2021 opening balance
-from GBP193,625,102 to GBP276,931,087 and in the FY2021 closing balance from GBP174,352,252 to
-GBP290,627,822. However, neither of those 'old-basis' figures matches FY2021's own originally-filed
-Annual Report, which itself shows an opening balance of GBP83,305,985 and a closing balance of
-GBP116,275,570 for FY2021 - a discrepancy in the source documents themselves that could not be
-traced or resolved. Per this project's convention, each year below uses its own originally-published
-figures (so FY2021's closing balance will not visually chain into FY2022's opening balance); this gap
-is flagged here rather than forced to reconcile, the same treatment as Arab Bank Europe's unexplained
-cash-bridge gap elsewhere in this project.
-Also note: FY2021's own 'Operating cash flows before movement in working capital' subtotal
-(GBP(10,764,152)) is GBP360 different from the sum of its own printed component lines - an immaterial
-source rounding artifact, not corrected.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6965,7 +7192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -7591,7 +7818,7 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
     </row>
-    <row r="34" ht="420" customHeight="1">
+    <row r="34" ht="409" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own key-metrics table, GBP '000 and percentages exactly as printed:
@@ -7603,20 +7830,36 @@
 FY2021: no KM1 in any edition - blank.
 GTBANK PRINTS THE TEMPLATE UNNUMBERED AND ABRIDGED. The table carries the template's section headings and row labels in the template's order but no template row numbers at all, so none are shown here - supplying them from the PRA template would put words in the Bank's mouth. It also omits whole blocks the template defines: no "Additional own funds requirements based on SREP" section (no UK 7a-UK 7d), no UK 8a / UK 9a / 10 / UK 10a buffer rows, no UK 14a-14f leverage block, and no "Leverage ratio total exposure measure" amount row - only the ratio. Those absences are the Bank's own row set, not gaps in transcription. GTBank also drifts in capitalisation between editions ("Total Capital Ratio (%)" in FY2024/FY2025 against "Total capital ratio (%)" in FY2023, and likewise the buffer rows); the labels above follow the most recent edition.
 EDITION PER COLUMN, AND WHY IT MATTERS MORE HERE THAN USUAL. Every edition prints two columns, the reporting year and the prior year, and GTBank RESTATES its prior-year column materially. Taking each year from the edition in which it is the reporting year is therefore not a formality: the FY2024 edition restates FY2023 RWAs from 105,275 to 108,387 (3.0%), the CET1/Tier 1/Total ratio from 32.34% to 32.30%, the leverage ratio from 6.00% to 8.30%, HQLA from 230,533 to 197,710, the overall capital requirement from 14.67% to 14.07% and CET1-available from 17.67% to 18.23%. This sheet carries the as-first-published figures throughout. The restated FY2023 comparatives are recorded on their own labelled rows of the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio, Total RWAs and Leverage Ratio sheets, so neither version is lost and neither overwrites the other.
-FY2022 COMES FROM THE FY2023 EDITION BECAUSE ITS OWN EDITION HAS NO KM1. The FY2022 Pillar 3 report predates the template: it presents bespoke tables instead - "Table 3: Eligible Capital", "Table 4: Capital Adequacy Ratio (CAR) %" and "Table 5: CRR Leverage Ratio %" - with no template row labels or section headings, and the string NSFR does not occur in that document at all. Confirmed by reading the PDF rather than by a text search alone: its three embedded images (pages 1, 6 and 12) were listed and are a cover logo, the leverage-ratio table that extracts fine as text, and a risk-category diagram - there is no key-metrics table hidden as a bitmap. FY2021 appears inside no KM1 in any edition, so it is blank here; the FY2021 figures elsewhere in this workbook come from the FY2022 edition's bespoke tables.
+FY2022 COMES FROM THE FY2023 EDITION BECAUSE ITS OWN EDITION HAS NO KM1. The FY2022 Pillar 3 report predates the template: it presents bespoke tables instead - "Table 3: Eligible Capital", "Table 4: Capital Adequacy Ratio (CAR) %" and "Table 5: CRR Leverage Ratio %" - with no template row labels or section headings, and the string NSFR does not occur in that document at all. Confirmed by reading the PDF rather than by a text search alone: its three embedded images (pages 1, 6 and 12) were listed and are a cover logo, the leverage-ratio table that extracts fine as text, and a risk-category diagram - there is no key-metrics table hidden as a bitmap. FY2021 appears inside no KM1 in any edition, so it is blank here; the FY2021 figures elsewhere in this workbook come from the FY2022 edition's bespoke tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="409" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 SOURCE DEFECT, REPRODUCED AND FLAGGED: THE CET1 CAPITAL ROW. GTBank prints "Common Equity Tier 1 ("CET1") capital  37,000" in every year of every edition - its paid-up share capital, unchanged since before this workbook's window - while the CET1 RATIO printed two rows below in the same column is struck on the Tier 1 / Total capital figure (FY2025: 54,604 / 148,821 = 36.69%, the printed ratio; 37,000 / 148,821 would be 24.86%). The Bank's own table is therefore internally inconsistent.
 A CONSTANT ACROSS FOUR YEARS IS NORMALLY A TRANSCRIPTION FAULT, SO THIS ONE WAS RE-INVESTIGATED FROM SCRATCH ON 16 SEPTEMBER 2026 BEFORE BEING ACCEPTED. Three candidate explanations were tested and all three were ruled out. (1) ROW MISALIGNMENT - ruled out by rendering each edition's page at 300 dpi and reading the ruled table cells directly rather than trusting `pdftotext`. That mattered: in the FY2025 edition the text layer emits the 2025 column of several rows on its own line ABOVE the row label (an artefact of vertical centring in taller cells), which is exactly what a column shift would look like. The rendered cell borders show it is not one - CET1 capital is a single-height row reading 37,000 | 37,000, while Tier 1 Capital and Total Capital read 54,604 | 48,075. The FY2024 and FY2023 editions have no vertical offset at all and print the same 37,000 in both of their columns. (2) A UNIT CHANGE BETWEEN EDITIONS - ruled out: all three editions head the table "Key Metrics (GBP '000')" and repeat "Amounts in GBP '000'" inside the header cell, so there is no unit break to mistake for a level shift. (3) THE TEMPLATE PRINTED TWICE ON TWO ENTITY BASES - ruled out: the key-metrics rows occur on exactly one page of each edition (FY2025 p.13, FY2024 p.14, FY2023 p.13), and the Bank states it has no subsidiaries in the UK or abroad, so there is no second basis to confuse.
 (4) A PARENT-LEVEL BLOCK READ BY MISTAKE - ruled out by the COLUMN HEADERS, which are the only thing that identifies an entity when a group and a subsidiary share a table. A constant that does not move while the entity's own capital moves is exactly what reading a parent column produces, so this was checked rather than assumed. GTBank's table is not of that shape: its two value columns are headed by DATES ("31st December 2025" and "31st December 2024"), not by entity names - there is no Group-beside-Individual split, no second table in an appendix, and the document is titled for Guaranty Trust Bank (UK) Limited throughout. Decisively, 37,000 is identified INSIDE THIS SAME DOCUMENT as the UK entity's own paid-up share capital by its section 7.1 build-up, which adds the UK entity's own P&amp;L reserve to it to reach the UK entity's own total capital. It is the right entity and the wrong LINE of that entity's build-up - a row-population error by the Bank, not a group-vs-subsidiary mix-up. The Nigerian parent (Guaranty Trust Bank Nigeria, under Guaranty Trust Holding Company) is outside the UK disclosure regime and publishes no UK KM1 for this subsidiary; nothing here is sourced from it.
 WHAT 37,000 ACTUALLY IS, from the Bank's own build-up. Each edition's section 7.1 "Table 4: Available Capital" derives capital as paid-up share capital 37,000 + Profit and Loss reserve 17,563 + fair value reserve 41 - intangibles nil = 54,604 "Total Capital Available" (FY2025 figures; FY2024 the same shape, 37,000 + 11,019 + 56 = 48,075), with Tier 2 and subordinated debt both nil, and the same section says in words that "Tier 1 Capital comprises paid-up share capital and the Profit &amp; Loss reserve less intangible assets". So the KM1 CET1 row has been populated with the FIRST LINE of that build-up instead of its total. That is the defect, and it is the Bank's, not this transcription's.
-BOTH FIGURES AND BOTH SOURCES, since the two sides of this workbook deliberately disagree. KM1 row = 37,000 in all four years, from the "Common Equity Tier 1 ("CET1") capital" row of Table 2 / "Key Metrics" in the FY2025 (p.13 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695), FY2024 (p.14 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481) and FY2023 (p.13 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289) editions. CET1 Capital sheet = 54,604,000 / 48,075,379 / 39,390,993 / 28,344,378, from each year's Annual Report Note 23.8(a) regulatory-capital table (https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0) and, for FY2025, from the FY2025 Pillar 3's own Table 4 "Total Capital Available" of 54,604 - the figure the ratios are actually struck on. The 37,000 is reproduced here unchanged because reproducing the template is the point of this sheet; NOTHING WAS EDITED ON EITHER SIDE TO MAKE THE TWO AGREE, and the four cross-check disagreements this raises in verify_workbook.py are expected and correct.
+BOTH FIGURES AND BOTH SOURCES, since the two sides of this workbook deliberately disagree. KM1 row = 37,000 in all four years, from the "Common Equity Tier 1 ("CET1") capital" row of Table 2 / "Key Metrics" in the FY2025 (p.13 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695), FY2024 (p.14 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481) and FY2023 (p.13 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289) editions. CET1 Capital sheet = 54,604,000 / 48,075,379 / 39,390,993 / 28,344,378, from each year's Annual Report Note 23.8(a) regulatory-capital table (https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0) and, for FY2025, from the FY2025 Pillar 3's own Table 4 "Total Capital Available" of 54,604 - the figure the ratios are actually struck on. The 37,000 is reproduced here unchanged because reproducing the template is the point of this sheet; NOTHING WAS EDITED ON EITHER SIDE TO MAKE THE TWO AGREE, and the four cross-check disagreements this raises in verify_workbook.py are expected and correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="409" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 ZERO GLYPHS. There are none: GTBank leaves no cell dashed or zeroed in this table. Every cell shown is a printed figure and every blank is a row or column the Bank did not print.
 LATEST-EDITION CHECK, 16 September 2026, against the Bank's own site rather than this script's citation list. gtbankuk.com publishes documents only from /about-gtbank-uk/our-company (the /investor-relations page renders no document links at all, in the HTML or in the sitemap). That page links exactly two reports: "GTBank-UK-Pillar-3-Disclosure-2025.pdf" and "GTBank-UK-Annual-Report-and-Financial-Statement-2024.pdf". The FY2025 Pillar 3 is the newest edition and is already cited here. Companies House (05969821) confirms the FY2025 Annual Report is not yet filed - the latest accounts are made up to 31 December 2024 - which is why FY2025 is Pillar 3-sourced throughout this workbook. Checked, none newer.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7628,7 +7871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7727,7 +7970,7 @@
       </c>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="91" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Note: UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
@@ -7735,7 +7978,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="170" customHeight="1">
+    <row r="8" ht="390" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
@@ -7764,8 +8007,15 @@
     is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
     while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
     section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
     Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
     ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
     same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
@@ -7793,7 +8043,14 @@
   Pillar 1 requirement                               8,368                         8,671
   HQLA (12m average, weighted)                     230,533                       197,710
   Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
 capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
 to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
@@ -7811,9 +8068,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7825,7 +8084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7930,14 +8189,14 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="170" customHeight="1">
+    <row r="8" ht="390" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
@@ -7966,8 +8225,15 @@
     is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
     while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
     section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total
-    Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
     Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
     ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
     same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
@@ -7995,7 +8261,14 @@
   Pillar 1 requirement                               8,368                         8,671
   HQLA (12m average, weighted)                     230,533                       197,710
   Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
 capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
 to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
@@ -8013,9 +8286,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
+++ b/banks/GUARANTY TRUST BANK UK FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2076,14 +2077,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
+          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2122,51 +2123,55 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 capital - Annual Report Note 23.8(a), exact to the pound</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075.379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390.993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344.378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089.641</v>
+          <t>CET1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 capital - as printed in the Pillar 3 Key Metrics table</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>48075</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>39391</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>28345</v>
-      </c>
+          <t>CET1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="117" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.
-UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
-ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2295,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -2336,55 +2341,51 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
+          <t>Tier 1 capital - Annual Report Note 23.8(a), exact to the pound</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075.379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390.993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344.378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089.641</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
+          <t>Tier 1 capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="117" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+          <t>Note: The Bank has no Additional Tier 1 capital, so Tier 1 capital equals CET1 capital.
+UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
         </is>
       </c>
     </row>
@@ -2508,14 +2509,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
+          <t>Guaranty Trust Bank (UK) Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2554,51 +2555,55 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total regulatory capital (unaudited) - Annual Report Note 23.8(a), exact to the pound</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>48075.379</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>39390.993</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>28344.378</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>25089.641</v>
+          <t>Tier 1 ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Total regulatory capital - as printed in the Pillar 3 Key Metrics table</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>54604</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>48075</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>39391</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>28345</v>
-      </c>
+          <t>Tier 1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="117" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.
-UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
-ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
         </is>
       </c>
     </row>
@@ -2722,14 +2727,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -2768,55 +2773,51 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total Capital Ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
+          <t>Total regulatory capital (unaudited) - Annual Report Note 23.8(a), exact to the pound</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>48075.379</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>39390.993</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>28344.378</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>25089.641</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
+          <t>Total regulatory capital - as printed in the Pillar 3 Key Metrics table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>54604</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>48075</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>39391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>28345</v>
+      </c>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="117" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
+          <t>Note: The Bank has no Tier 2 capital, so Total Capital equals Tier 1 capital equals CET1 capital.
+UNIT (changed 2026-09-18). This sheet is in GBP'000, matching the Total RWAs, RWA Breakdown and KM1 sheets of this workbook. It was previously published in pounds, which was correctly labelled and correctly transcribed but left this figure 1,000x out of scale against the RWA sheet a reader would divide it by. No figure was rescaled to achieve this: row 1 is the Annual Report amount with its pence retained (FY2024's 48,075,379 exactly, written as 48,075.379), so no precision was lost.
+ROW 2 is the Bank's own printed GBP'000 figure from the Pillar 3 Key Metrics table. It is shown separately rather than merged because the two sources DISAGREE at FY2022: the Annual Report gives 28,344.378 and the Pillar 3 prints 28,345, a difference of about GBP 622. FY2024 and FY2023 round exactly to the printed figure; FY2022 does not. FY2022 is also the only year taken from the FY2023 edition's comparative column rather than from its own edition. Neither figure is corrected to the other.</t>
         </is>
       </c>
     </row>
@@ -2940,14 +2941,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2986,35 +2987,47 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>148821</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>157370</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>105275</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>100287</v>
+          <t>Total Capital Ratio (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>36.69%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>26.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32.34%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>20.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25.02%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
+          <t>Total Capital Ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n">
-        <v>108387</v>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>32.30%</t>
+        </is>
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
@@ -3022,7 +3035,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
         </is>
       </c>
     </row>
@@ -3132,323 +3145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5; FY2023 likewise derived but on the FY2024 edition's RESTATED FY2023 basis, in its own separate block - the Bank publishes no FY2023 risk-type split anywhere. Do not mix figures across the three blocks - see the sources note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£'000)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n">
-        <v>166793</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>77962</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>20026</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>22148</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n">
-        <v>215</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
-        <v>187034</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>100287</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>98212.5</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>113012.5</v>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>275</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>50337.5</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>44187.5</v>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA (derived)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>148825</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>157375</v>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>FY2023 only — Pillar 1 capital requirement × 12.5 on the FY2024 edition's RESTATED FY2023 basis (108,387), NOT the as-first-published 105,275 — see sources note</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Credit risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n">
-        <v>75462.5</v>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Market risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n">
-        <v>32762.5</v>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Total RWA (derived, FY2023 restated basis)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n">
-        <v>108387.5</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="20" ht="390" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
-FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
-    FY2023 ADDED 2026-09-18, ON EXACTLY THOSE TERMS. The paragraph above set the conditions and they are met here, so FY2023 now carries its own SEPARATE section rather than being merged into the FY2025/FY2024 derived block: the figures are the FY2024 edition's RESTATED FY2023 capital requirements x 12.5 (Credit 6,037 -&gt; 75,462.5; Market 13 -&gt; 162.5; Operational 2,621 -&gt; 32,762.5; total 108,387.5), every row label says 'restated basis', and the derived total is checked against that same edition's own restated FY2023 Total Risk-Weighted Exposure Amount of 108,387 - a gap of 0.5, pure GBP'000 rounding. It is deliberately NOT checked against the as-first-published 105,275, which remains the primary FY2023 row on the Total RWAs sheet and belongs to a different basis. The two sit in different sections of this sheet for that reason; a reader must not add a figure from the restated block to one from the as-disclosed block. Nothing about the underlying finding has changed: the Bank still publishes no FY2023 RWA split by risk type in any document, and every figure in this section is derived, never disclosed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="280" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-(2026-09-18 FOURTH check, this time OUTSIDE the Pillar 3 series - the one place the three prior verifications had not looked. The Bank's own FY2023 ANNUAL REPORT AND FINANCIAL STATEMENTS (Companies House company 05969821, accounts made up to 31 December 2023, filed 25 June 2024) contains no risk-weighted asset amount at all, let alone a split: its note 23.8(a) 'Regulatory capital (unaudited)' prints only Tier 1 capital components and Total regulatory capital (39,390,993, against 28,344,378 for 2022), and its KPI table gives the CET1 ratio as a percentage (32.3%, 2022: 24.6%) with no denominator. The report is an IMAGE-ONLY SCAN (go-tiff2pdf, 71 pages, every page an image, zero-character text layer), so it was read by full-document OCR; positive control on the OCR output, 70 occurrences of 'capital' and 112 of 'ratio' against 0 of '105,275', 0 of '108,387' and 0 of any 'risk weighted assets' table. This closes the last plausible primary source: the FY2023 split does not exist in the Annual Report either.)
-(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
-(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
-(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3462,14 +3159,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
+          <t>Guaranty Trust Bank (UK) Limited — Total RWAs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -3508,83 +3205,48 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Leverage Ratio (as first published in each year's own Pillar 3 report) - the Bank's Key Metrics row is LABELLED 'excluding claims on central banks' but prints the same value as its own narrative ratio in every edition, i.e. no exclusion is actually made; see note</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>9.11%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>8.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>4.38%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
+          <t>Total risk-weighted exposure amount (as first published)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>148821</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>157370</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>105275</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>100287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+          <t>Total risk-weighted exposure amount - FY2023 as restated in the FY2024 Pillar 3 edition</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>8.30%</t>
-        </is>
+      <c r="D5" s="7" t="n">
+        <v>108387</v>
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="299" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
-  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
-  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
-  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
-FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.
-ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
-HOW THAT WAS ESTABLISHED: all 6 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (6 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. No edition contained either. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
-THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="390" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023 appears twice because the two editions disagree materially and neither is allowed to overwrite the other. 105,275 is the figure in the FY2023 Pillar 3 report's own Key Metrics table (read as a primary source 2026-09-15); 108,387 is the restated FY2023 comparative in the FY2024 edition. The restatement is not a rounding difference - it is 3.0% - and it is the restated figure, not the original, that reconciles exactly to the Bank's own disclosed Pillar 1 capital requirement (8,671 x 12.5 = 108,387.5, against 8,368 x 12.5 = 104,600 on the original basis versus 105,275 printed). See the RWA Breakdown sheet for what this means for the FY2023 risk-type split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="390" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -3616,8 +3278,8 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="403" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="10" ht="403" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>(continued)
 Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
@@ -3652,8 +3314,8 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="182" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="12" ht="182" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>(continued)
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
@@ -3674,10 +3336,326 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 disclosures, £'000. FY2022/FY2021 as directly disclosed; FY2025/FY2024 derived from disclosed Pillar 1 capital requirement x 12.5; FY2023 likewise derived but on the FY2024 edition's RESTATED FY2023 basis, in its own separate block - the Bank publishes no FY2023 risk-type split anywhere. Do not mix figures across the three blocks - see the sources note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Standalone Pillar 3 — risk-weighted assets, as disclosed</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>166793</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>77962</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>20026</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>22148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>187034</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>100287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>98212.5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>113012.5</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>50337.5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>44187.5</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>148825</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>157375</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>FY2023 only — Pillar 1 capital requirement × 12.5 on the FY2024 edition's RESTATED FY2023 basis (108,387), NOT the as-first-published 105,275 — see sources note</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Credit risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>75462.5</v>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Market risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>32762.5</v>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total RWA (derived, FY2023 restated basis)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n">
+        <v>108387.5</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="20" ht="390" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO):
+FY2022 &amp; FY2021 (directly disclosed as risk-weighted assets, not derived): GTBank UK Pillar 3 Disclosures 2022, section 2.4 'Risk-Weighted Assets (RWAs)' table (Total/Credit/Operational/Market RWA) - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2025 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2025, Table 5 'Minimum Capital Requirement ("MCR")', p.16 (Credit Risk 7,857 / Market Risk 22 / Operational Risk 4,027, GBP'000, summing to the same table's own printed Pillar 1 requirement of 11,906) - each figure below is that capital requirement divided by 8% (x12.5), the exact Basel/CRR Article 92 identity, not an estimate. Derived total 148,825 vs the same document's own separately disclosed Total Risk-Weighted Exposure Amount of 148,821 - a gap of 4 (0.003%), comfortably inside the +/-19 maximum attributable to GBP'000 rounding of three components, so the x12.5 identity reconciles cleanly for this year (unlike FY2023, see below) - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024 (derived, not directly disclosed as RWA): GTBank UK Pillar 3 Disclosure 2024, Table 5 'Minimum Capital Requirement ("MCR")', p.14, only discloses the Pillar 1 MINIMUM CAPITAL REQUIREMENT by risk type - so each category figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity, not an estimate. Reconciles to within £5k of the Total RWAs sheet's own FY2024 figure (157,370) - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: checked against the FY2023 Pillar 3 report itself and still NOT added. THE BANK PUBLISHES NO FY2023 RWA BREAKDOWN BY RISK TYPE ANYWHERE - this is a disclosure gap in the source, not a research gap. The FY2023 report's section 6.4 'Risk-Weighted Assets' (p.15) merely names the three categories in prose and prints no table; its Key Metrics table (pp.13-14) gives a single aggregate Total Risk-Weighted Exposure Amount of 105,275 with no split; and the only category-level figures in the entire document are CAPITAL REQUIREMENTS (section 7.3, p.17: Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643, GBP'000), never RWAs - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+    On the original FY2023 basis the x12.5 identity does not reconcile: 8,368 x 12.5 = 104,600 against the same report's own printed 105,275, a gap of 675 (0.6%), far beyond the +/-19 attributable to GBP'000 rounding of three components. On the FY2024 edition's RESTATED FY2023 basis it reconciles exactly (Credit 6,037 / Market 13 / Operational 2,621 = 8,671; 8,671 x 12.5 = 108,387.5 against that edition's own restated FY2023 RWA of 108,387). FY2023 is nonetheless still left blank here, for two reasons: (a) the derived rows would have to sit on the restated 108,387 basis while the Total RWAs sheet's primary FY2023 row is the as-first-published 105,275, silently mixing two bases in one column - exactly the trap this workbook's convention exists to avoid; and (b) no FY2023 figure in either edition is a disclosed RWA. If a future pass decides the derived basis is acceptable for FY2023, it must add the row under the restated total, label it as such, and not reconcile it against 105,275.
+    FY2023 ADDED 2026-09-18, ON EXACTLY THOSE TERMS. The paragraph above set the conditions and they are met here, so FY2023 now carries its own SEPARATE section rather than being merged into the FY2025/FY2024 derived block: the figures are the FY2024 edition's RESTATED FY2023 capital requirements x 12.5 (Credit 6,037 -&gt; 75,462.5; Market 13 -&gt; 162.5; Operational 2,621 -&gt; 32,762.5; total 108,387.5), every row label says 'restated basis', and the derived total is checked against that same edition's own restated FY2023 Total Risk-Weighted Exposure Amount of 108,387 - a gap of 0.5, pure GBP'000 rounding. It is deliberately NOT checked against the as-first-published 105,275, which remains the primary FY2023 row on the Total RWAs sheet and belongs to a different basis. The two sit in different sections of this sheet for that reason; a reader must not add a figure from the restated block to one from the as-disclosed block. Nothing about the underlying finding has changed: the Bank still publishes no FY2023 RWA split by risk type in any document, and every figure in this section is derived, never disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="280" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+(2026-09-18 FOURTH check, this time OUTSIDE the Pillar 3 series - the one place the three prior verifications had not looked. The Bank's own FY2023 ANNUAL REPORT AND FINANCIAL STATEMENTS (Companies House company 05969821, accounts made up to 31 December 2023, filed 25 June 2024) contains no risk-weighted asset amount at all, let alone a split: its note 23.8(a) 'Regulatory capital (unaudited)' prints only Tier 1 capital components and Total regulatory capital (39,390,993, against 28,344,378 for 2022), and its KPI table gives the CET1 ratio as a percentage (32.3%, 2022: 24.6%) with no denominator. The report is an IMAGE-ONLY SCAN (go-tiff2pdf, 71 pages, every page an image, zero-character text layer), so it was read by full-document OCR; positive control on the OCR output, 70 occurrences of 'capital' and 112 of 'ratio' against 0 of '105,275', 0 of '108,387' and 0 of any 'risk weighted assets' table. This closes the last plausible primary source: the FY2023 split does not exist in the Annual Report either.)
+(2026-09-12 independent re-verification: re-fetched this exact document and re-read section 5.2 'Key Prudential Metrics' [Total Risk-Weighted Exposure Amount 105,275, single aggregate figure, no category split] and section 7.3 'Minimum Capital Requirement - Pillar 1' [Credit Risk 5,712 / Market Risk 13 / Operational Risk 2,643] directly - confirms this analysis exactly, no cleaner reconciling source exists anywhere else in the document. This remains a genuine internal inconsistency in the Bank's own filing, not a research gap.)
+(2026-09-15 THIRD verification, re-reading the full FY2023 document rather than the prior notes. Confirms FY2023 stays out, and strengthens the case: section 6.4 'Risk-Weighted Assets' is narrative only [it names the three categories but publishes no table], and the ONLY category-level figures anywhere in the document are capital requirements, never RWAs. The FY2023 credit MCR of 5,712 is itself internally sound - section 8.3 breaks it into exposure classes that sum to it exactly [Financial Institutions 2,830 + Retail 4 + Corporate 0 + Secured against Real Estate 1,612 + Fixed and Other Assets 1,266 = 5,712] - so the 675 gap cannot be pinned on a misprinted credit figure and remains unexplained. Do not add FY2023 on the x12.5 basis.)
+(2026-09-15 SEPARATE FINDING, recorded here because it was found in the same document and bears on FY2022's reliability rather than FY2023's: the FY2023 report's own FY2022 COMPARATIVE column misprints the credit risk MCR as 9,343. The FY2022 figures carried in this sheet are NOT affected and are correct - they come from the FY2022 report's own directly-disclosed RWA table, they sum exactly to the FY2022 total of 187,034, and that total is independently confirmed by this FY2023 document's own comparative column. The FY2022 operational and market MCRs also reconcile cleanly on x12.5 [1,602 -&gt; 20,025 vs 20,026 disclosed; 17 -&gt; 212.5 vs 215 disclosed]. Only credit does not: 9,343 x 12.5 = 116,788 against the disclosed 166,793, whereas the disclosed RWA implies an MCR of 13,343.44 - a difference of almost exactly 4,000, the signature of a leading-digit transcription error [13,343 printed as 9,343] in the comparative. Flagged so that a future pass does not 'correct' this sheet's sound FY2022 figures to match a misprinted comparative.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3689,7 +3667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3703,7 +3681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+          <t>Guaranty Trust Bank (UK) Limited — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -3749,46 +3727,83 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
+          <t>Leverage Ratio (as first published in each year's own Pillar 3 report) - the Bank's Key Metrics row is LABELLED 'excluding claims on central banks' but prints the same value as its own narrative ratio in every edition, i.e. no exclusion is actually made; see note</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>197%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>309%</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>250%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>274%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>356%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="130" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
-DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
-By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="390" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>5.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as restated in the FY2024 and FY2025 Pillar 3 editions</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>8.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>FY2023 as printed in the FY2023 report's own Key Metrics table (contradicted - see note)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="299" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note: FY2023 carries three rows because the Bank publishes three different numbers for it, and none is allowed to overwrite another.
+  Row 1, 8.29%: the FY2023 Pillar 3 report's own section 7.6 (p.17), which shows its working - Tier 1 capital GBP39,390,993 against total on- and off-balance-sheet footings of GBP475,263,939. That division reproduces 8.29% exactly, and the Tier 1 figure ties to this workbook's own FY2023 Tier 1 Capital sheet and Balance Sheet Total equity. This is the as-first-published basis used for every other year in row 1.
+  Row 2, 8.30%: the same measure in the FY2024 and FY2025 editions, which restate the footings to GBP474,761,920 (Tier 1 unchanged at GBP39,390,993). A GBP502,019 restatement of the denominator, worth one basis point. This is the value this workbook carried before 2026-09-15, when it was sourced from the FY2024 edition's comparative rather than from the FY2023 report itself.
+  Row 3, 6.00%: the figure printed in the FY2023 report's own Key Metrics table, in the row labelled 'Leverage ratio excluding claims on central banks (%)'. It is NOT used as the headline because it is contradicted by that same report's narrative one page later and is not reproducible from any pair of figures the report discloses; and because in the FY2022, FY2024 and FY2025 editions that identically-labelled row always prints exactly the same value as that edition's narrative leverage ratio (4.38%, 8.02%, 9.11% respectively), i.e. the Bank never actually excludes central bank claims in it. It is recorded rather than discarded.
+FY2025 (9.11%) is taken from the FY2025 report's Key Metrics table, NOT from its section 7.6 narrative, which was left unrevised from the prior edition and still quotes the 31 December 2024 position (8.02%). See note (3) in the source citation below.
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 6 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (6 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. No edition contained either. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="390" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
 FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
@@ -3820,8 +3835,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="403" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="403" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>(continued)
 Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
@@ -3856,8 +3871,8 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="182" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="182" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>(continued)
 verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
@@ -3878,6 +3893,210 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>197%</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>309%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>250%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>274%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>356%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Note: Every year is the Bank's own disclosed headline LCR, taken as printed from the Key Metrics table. Basis is consistent across editions: the FY2024 value printed in the FY2025 report's comparative column (309%) matches the FY2024 report's own figure exactly, and likewise FY2023 (250%) between the FY2024 and FY2023 editions.
+DO NOT RE-DERIVE THESE FROM THE PUBLISHED COMPONENTS. The Bank's own LCR component rows do not reconcile to its own printed ratio in ANY year, consistently and by a wide margin: FY2025 HQLA 228,692 / net outflows 234,753 = 97%, not the printed 197%; FY2024 188,372 / 42,483 = 443%, not 309%; FY2023 230,533 / 74,454 = 310%, not 250% (all GBP'000; the FY2023 HQLA figure here is from the FY2023 report itself, read 2026-09-15 - the FY2024 edition restates it to 197,710, which gives 266%, also not 250%, so the mismatch survives the restatement). The component arithmetic is internally sound - gross outflows less inflows does equal the stated net outflows every year - so the mismatch is between the components and the ratio, not within the components. The likely cause is a mixed basis: the HQLA row is explicitly labelled 'average of last 12mths' while the ratio appears to be struck on a different (probably year-end) basis. The disclosed ratio is used here because it is the Bank's own headline figure and the only one comparable across years and across banks in this project; no attempt is made to correct or recompute it.
+By contrast the NSFR components DO reconcile exactly every year (see that sheet), which is why this caveat is specific to LCR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="390" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="403" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="182" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -3887,7 +4106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4075,196 +4294,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A7:E7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2025 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2024 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2023 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3, which carries the FY2021 comparatives (text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="390" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="403" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="182" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4909,6 +4938,196 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in the FY2025 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in the FY2024 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in the FY2023 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3 (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in the FY2022 GTBank UK Pillar 3, which carries the FY2021 comparatives (text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="390" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
+FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
+Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
+Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
+FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
+FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
+section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
+table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
+        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
+        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
+FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
+FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
+the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
+These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
+and (from FY2022, via that comparative) NSFR.
+MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
+(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
+FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
+The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
+regulatory capital throughout; the same figure is used on all three sheets below.
+FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
+(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
+    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
+    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
+    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
+    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
+    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="403" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
+    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
+    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
+    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
+(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
+    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
+    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
+    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
+    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
+(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
+    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
+    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
+    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
+    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
+    taken from those tables, never from the stale narrative paragraphs.
+FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
+primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
+column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
+workbook's sheets, on separate labelled rows, rather than one overwriting the other:
+                                        FY2023 as first published   FY2023 as restated in FY2024 edition
+  Total risk-weighted exposure amount              105,275                       108,387
+  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
+  Leverage ratio (narrative basis)                   8.29%                         8.30%
+  Credit risk MCR                                    5,712                         6,037
+  Operational risk MCR                               2,643                         2,621
+  Pillar 1 requirement                               8,368                         8,671
+  HQLA (12m average, weighted)                     230,533                       197,710
+  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
+CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="182" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
+capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
+to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
+share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
+194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
+NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
+says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
+GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
+FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
+narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
+row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
+(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
+sheet, which carries all three on separate rows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7192,6 +7411,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranty Trust Bank (UK) Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>19.75%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>30.73%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>14.50%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>17.97%</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>26.42%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>13.67%</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>-33.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Return on Equity Ratio (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>19.75%</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="247" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on Equity Ratio: “The ratio of profit for the year (before tax) to average equity, expressed as a percentage.”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2023, where return on equity is 30.73% on an average basis and 26.42% on a year-end basis.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2023 Return on Equity Ratio 30.73%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year” and the Balance Sheet rows “shareholders' funds (total equity)” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Guaranty Trust Bank (UK) Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Guaranty Trust Bank (UK) Limited's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘GUARANTY TRUST BANK UK’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7865,7 +8299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8076,222 +8510,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Guaranty Trust Bank (UK) Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>CET1 ratio (as first published)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>36.69%</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>26.89%</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>32.34%</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>20.68%</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>25.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>CET1 ratio - FY2023 as restated in the FY2024 Pillar 3 edition</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>32.30%</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Note: Row 1 is each year as first published, in that year's own Pillar 3 report's Key Metrics table. Row 2 records that the FY2024 edition restates its FY2023 comparative to 32.30% (alongside restating FY2023 RWAs from 105,275 to 108,387 - see the Total RWAs sheet). Neither figure is overwritten by the other. Note that the Bank's printed ratio does not reconcile to its own capital and RWA on either basis (39,391 / 105,275 = 37.42%; 39,391 / 108,387 = 36.34%); both values are transcribed exactly as printed and no attempt is made to recompute them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="390" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Guaranty Trust Bank (UK) Limited's own standalone Pillar 3 disclosures (not GTBank Nigeria or GTCO).
-FY2025: 'Pillar 3 Disclosure 2025' (as at 31 December 2025), section 5.2 'Key Prudential Metrics'
-Table 2 pp.12-13, section 7.1 'Available Capital' Table 4 p.15, section 7.3 'Minimum Capital
-Requirement' Table 5 p.16 - https://gtbank-uk.files.svdcdn.com/production/download/GTBank-UK-Pillar-3-Disclosure-2025.pdf?dm=1784815695
-FY2024: Key Metrics pp.14-15, Available Capital/MCR pp.16-18 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-Disclosure-2024.pdf?dm=1769088481
-FY2023: 'GTBank UK Pillar 3 Disclosures 2023', section 5.2 'Key Prudential Metrics' table pp.13-14,
-section 7.1 'Available Capital' table p.16, section 7.3 'Minimum Capital Requirement - Pillar 1'
-table p.17, section 7.6 'Leverage' narrative p.17 - https://gtbank-uk.files.svdcdn.com/production/general/GTBank-UK-Pillar-3-2023.pdf?dm=1731585289
-        (a second, identical copy of the same FY2023 document is also live at https://gtbank-uk.files.svdcdn.com/production/general/GTBUK-Pillar-3-2023.pdf;
-        it differs only in pagination - 27 pages instead of 26 - and carries no differing figure.)
-FY2022: KPI/Eligible Capital/CAR/Leverage pp.4-6 and MCR/TCR pp.14-16 - https://gtbank-uk.files.svdcdn.com/production/media/GTBUK-Pillar-3-2022.pdf
-FY2021 is included as the comparative column in the FY2022 disclosure; FY2022's NSFR (the one metric
-the FY2022 edition never reports) is taken from the FY2023 edition's own FY2022 comparative column.
-These disclosures provide CET1, Tier 1 and total capital, RWA, capital ratios, leverage ratio, LCR
-and (from FY2022, via that comparative) NSFR.
-MREL is not numerically disclosed in any of the reviewed standalone reports, the FY2025 one included
-(the FY2025 document contains no occurrence of 'MREL' or 'minimum requirement for own funds' at all).
-FY2024/FY2023 also cross-check the statutory accounts' regulatory-capital Note 23.8(a) - https://find-and-update.company-information.service.gov.uk/company/05969821/filing-history/MzQ2NTE3NTM2NmFkaXF6a2N4/document?format=pdf&amp;download=0.
-The Bank states it has no Additional Tier 1 capital, so Common Equity Tier 1 = Tier 1 = Total
-regulatory capital throughout; the same figure is used on all three sheets below.
-FY2025 DATA-QUALITY NOTES (read before using the FY2025 column):
-(1) CET1 basis. The FY2025 Key Metrics table's own 'Common Equity Tier 1 ("CET1") capital' row prints
-    37,000 for BOTH 2025 and 2024 - that is the Bank's paid-up share capital, not its CET1 capital, and
-    is an internal error in the Bank's own table (the FY2024 report prints the same 37,000 in that row
-    while its own leverage narrative states Tier 1 capital of GBP48,075,379). The same document's
-    section 7.1 'Available Capital' table builds capital from paid-up share capital 37,000 + P&amp;L reserve
-    17,563 + fair value reserve 41 - intangibles nil = 54,604, labelled 'Sub-Total' and then 'Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="403" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-Capital Available' with Tier 2 and subordinated debt both nil; section 7.3 repeats 54,604 as 'Total
-    Capital Resource'. 54,604 is used here for CET1/Tier 1/Total Capital, which also ties the disclosed
-    ratio exactly: 54,604 / 148,821 = 36.69%, the ratio printed in the Key Metrics table. This is the
-    same treatment already applied to FY2024 (37,000,000 + 11,019,326 + 56,053 = 48,075,379).
-(2) FY2025 precision. The FY2025 capital figure is only available at GBP'000 precision (54,604) because
-    no FY2025 Annual Report has been filed with Companies House yet (due 30 Sep 2026), so the exact
-    pound figure from Note 23.8(a) that every earlier year uses does not exist for FY2025. The CET1/
-    Tier 1/Total Capital sheets therefore show FY2025 as 54,604,000 - the disclosed thousands figure
-    scaled, not an exact-to-the-pound amount. Earlier years remain exact to the pound.
-(3) Stale prose in the FY2025 document. Its section 7.6 'Leverage' narrative and section 7.4 still refer
-    to '31st December 2024' and 'during 2024' - unrevised copy carried over from the prior edition. Its
-    numeric tables ARE updated (Table 1 financial performance, Table 2 key metrics, Table 4 available
-    capital and Table 5 MCR each carry a distinct 2025 column alongside the 2024 comparative, and the
-    2024 comparatives match this workbook's existing FY2024 figures exactly). All FY2025 values here are
-    taken from those tables, never from the stale narrative paragraphs.
-FY2023 RESTATEMENT (recorded 2026-09-15, when the FY2023 Pillar 3 report itself was obtained and read as a
-primary source for the first time - until then FY2023 was carried from the FY2024 edition's comparative
-column). The FY2024 edition materially RESTATES its FY2023 comparative. Both bases are shown on this
-workbook's sheets, on separate labelled rows, rather than one overwriting the other:
-                                        FY2023 as first published   FY2023 as restated in FY2024 edition
-  Total risk-weighted exposure amount              105,275                       108,387
-  CET1 / Tier 1 / Total capital ratio               32.34%                        32.30%
-  Leverage ratio (narrative basis)                   8.29%                         8.30%
-  Credit risk MCR                                    5,712                         6,037
-  Operational risk MCR                               2,643                         2,621
-  Pillar 1 requirement                               8,368                         8,671
-  HQLA (12m average, weighted)                     230,533                       197,710
-  Cash outflows (weighted)                         199,752 -- unchanged --        199,752
-CONFIRMED UNCHANGED between the two editions, so the following FY2023 figures in this workbook are now</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="182" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-verified against the primary source and not merely against a later comparative: Tier 1 capital and Total
-capital 39,391 (GBP'000; the FY2023 report's section 7.6 gives the exact figure GBP39,390,993, which ties
-to the FY2023 Balance Sheet's own Total equity), CET1 capital row printed as 37,000 in both (the known
-share-capital-not-CET1 error), total net cash outflows 74,454, LCR 250%, NSFR 310% with its components
-194,572 / 62,864, and the capital-conservation (2.50%) and countercyclical (2.00%) buffers.
-NOT CONFIRMED: the leverage ratio of 8.30% previously carried here. The FY2023 report's own section 7.6
-says 8.29%, computed there from Tier 1 GBP39,390,993 against total on- and off-balance-sheet footings of
-GBP475,263,939; the FY2024 edition restates those footings to GBP474,761,920 and so prints 8.30%. The
-FY2023 report's own Key Metrics table is a third value again, 6.00%, which is contradicted by its own
-narrative on the very next page and is not reproducible from any pair of figures it discloses - the same
-row in the FY2022, FY2024 and FY2025 editions always equals that edition's narrative leverage ratio
-(4.38%, 8.02%, 9.11%), so the FY2023 6.00% is an error in the Bank's own table. See the Leverage Ratio
-sheet, which carries all three on separate rows.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>